--- a/results/BTu_GSE4290_13_5_5.xlsx
+++ b/results/BTu_GSE4290_13_5_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
   <si>
     <t>classifier</t>
   </si>
@@ -73,205 +73,181 @@
     <t>POM_enGROUPS</t>
   </si>
   <si>
+    <t>POM_ALG</t>
+  </si>
+  <si>
+    <t>POM_ENTROPY</t>
+  </si>
+  <si>
     <t>RND_FST</t>
   </si>
   <si>
-    <t>POM_ENTROPY</t>
-  </si>
-  <si>
-    <t>POM_ALG</t>
-  </si>
-  <si>
     <t>SVC</t>
   </si>
   <si>
+    <t>3NN_OVO</t>
+  </si>
+  <si>
     <t>7NN_OVR</t>
   </si>
   <si>
     <t>7NN_MUL</t>
   </si>
   <si>
-    <t>3NN_OVO</t>
-  </si>
-  <si>
     <t>5NN_OVO</t>
   </si>
   <si>
+    <t>BAGGNG</t>
+  </si>
+  <si>
+    <t>5NN_OVR</t>
+  </si>
+  <si>
+    <t>5NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_OVR</t>
+  </si>
+  <si>
     <t>7NN_OVO</t>
   </si>
   <si>
-    <t>5NN_OVR</t>
-  </si>
-  <si>
-    <t>5NN_MUL</t>
-  </si>
-  <si>
-    <t>BAGGNG</t>
-  </si>
-  <si>
-    <t>3NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_OVR</t>
+    <t>1NN_OVO</t>
+  </si>
+  <si>
+    <t>DEC_TRE</t>
   </si>
   <si>
     <t>MLP</t>
   </si>
   <si>
-    <t>1NN_OVO</t>
-  </si>
-  <si>
     <t>1NN_MUL</t>
   </si>
   <si>
     <t>1NN_OVR</t>
   </si>
   <si>
-    <t>DEC_TRE</t>
-  </si>
-  <si>
     <t>A7</t>
   </si>
   <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
     <t>A2</t>
   </si>
   <si>
+    <t>A9</t>
+  </si>
+  <si>
     <t>A10</t>
   </si>
   <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
     <t>A5</t>
   </si>
   <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
     <t>xuyager</t>
   </si>
   <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.52707195347108, 2.027992306233598, 2.0921382999712494, 3.826475087033043, 2.1121640904649244, 2.9884195046557003, 3.8399832097283366, 2.5361137246635534, 1.3842857650354752, 1.6520204105430751, 2.9071340461094697, 1.2602469524036872, 1.3260933289140466, 2.4707630355143113, 1.5122794901980368, 1.8050464924235403, 1.7462395956793486, 3.749658300759141, 1.6408461148451587, 1.2424776897112955], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8596949218252029, 0.8369302588992195, 0.8067637350430865, 0.894507076309016, 0.8769125923069013, 0.8523650366239738, 0.9211091169186634, 0.8929527238772014, 0.860604908909654, 0.8416787597332093, 0.8195506532368403, 0.7961871426053247, 0.8609529196839952, 0.7658532500161485, 0.7627433489908344, 0.8556757612359891, 1.2200837297852472, 0.7950323112340134, 0.8333410704460817, 0.8204558166274252], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8250007060331693, 0.830349221807965, 0.7898089645783153, 0.8545578183186651, 0.8836734178060891, 0.8490292131527075, 0.8999527192768132, 0.8857966661704727, 0.8523114105662493, 0.8238370348665792, 0.8265113064105856, 0.7750203401745865, 0.8432222471799706, 0.7702486622361369, 0.7688804340115573, 0.8548894293878938, 0.8188668452734594, 0.8054066810678638, 0.8057966708465584, 0.8186710685389051], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.882438836213467, 1.4820147513460928, 1.2179038264742352, 1.06424849539806, 1.3064716819419586, 1.205600143866732, 3.3782770456108255, 1.1943796158226099, 2.3806260495207314, 1.1643071632295623, 1.4636918573413766, 1.4208022068687813, 1.4973462372157718, 2.0353977138707067, 2.7656847066620127, 1.3105104374801757, 2.489940324159525, 1.227762930685032, 2.001242495033579, 0.9941831630601126], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.1151311038721425, 1.5128651448329105, 2.057224187925083, 1.2009041387801653, 1.1866065754941157, 1.006247368694396, 1.2975321630394956, 1.2639881159531388, 1.0846974105675937, 0.8784713782069589, 1.1655237504700418, 0.856995386549768, 0.9362442663203838, 1.110406019388214, 0.8006257945134856, 1.1670332848462772, 0.9970444965924983, 0.9386865995698987, 1.4074435945986332, 1.1740952977923547], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.4371999969801952, 3.6429292740430492, 2.025927538581578, 1.2145499643072522, 1.3990449059383843, 0.994151894483075, 2.626946973251151, 2.433166818876066, 1.0186659947132632, 1.769275957264649, 1.2761671868470998, 1.2541518471786888, 1.3637092783299174, 1.1239714581344893, 1.0671502826334396, 1.3875885475137986, 1.0600974096872677, 2.2011087208014435, 1.5483754543617778, 0.8416894068404377], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8884452505420403, 0.8234732838521245, 0.8141287437350828, 0.9763205233719738, 0.8885285385262884, 0.9018482405040298, 1.0290418243989379, 0.985779077949992, 0.843453078363943, 0.9294094789618732, 0.918102762918857, 0.8071049723950621, 0.928167624817176, 0.891055348368475, 0.7732438520979876, 1.0117686993087394, 0.8265299682640966, 0.8604096391214605, 0.8722142448435278, 0.8016422193006256], \'SVC(C=1, random_state=13)\': [0.9488115709041645, 1.0898991369644198, 0.9590191805128369, 1.0033480961944354, 1.0140983776239143, 1.0367241125228033, 1.0590207197713102, 1.0079778959758383, 0.9929475995326538, 1.0384607082374202, 0.9485496194610622, 1.0232804696123696, 0.9994485607423254, 0.9811811457128748, 0.9445386596467275, 1.070535720117628, 0.9741609801464015, 1.014348355032505, 0.9913136919973087, 0.9838527199919854], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9222535691823563, 0.8854612502935924, 0.812706094523894, 0.9620639921842344, 0.8654739756887827, 0.911708673578104, 1.0478156316288336, 1.0350998125922015, 0.8586310633743351, 0.8575933029771339, 0.9217192345052102, 0.8332403222093299, 0.8958053479867893, 0.9445940087474196, 0.7691036698673323, 1.0154640897830471, 0.8391761480074511, 0.8830889985000077, 0.8974720944956943, 0.7804522646710089], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751435, 12.90451788005429, 16.909368256622862, 12.90451788005429, 14.684451380751431, 13.794484630402863, 12.90451788005429, 13.794484630402863, 16.464384881448577, 13.794484630402863, 14.684451380751431, 14.23946800557715, 10.67960100418286, 14.684451380751435, 13.794484630402863, 13.794484630402863, 15.129434755925718, 15.574418131100005, 14.239468005577146, 12.90451788005429], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.010525305477481, 6.959743332495877, 6.226241401327935, 6.959743332495877, 5.742666201101688, 6.574828862226504, 8.286136085419228, 5.71763749072464, 7.9225313982944305, 6.582575530696165, 7.82968711454281, 5.359038545675254, 5.71763749072464, 7.43476116012262, 6.106914295647953, 7.921887990872962, 6.1390462670731925, 10.043949098841951, 6.118379891350085, 4.794084657399516], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.8255747790911787, 4.464207905471744, 2.8461017226338075, 4.847331585657187, 3.635419706589437, 3.2120528434485798, 5.805675698792983, 3.2388723439095575, 4.5364875095796275, 4.932319718402431, 6.172198480593618, 3.3055983487933305, 3.261285627808882, 3.613241405143357, 3.6230277784141425, 4.965152911420798, 4.922154869807185, 5.808569989631661, 4.068361764384993, 3.140920622003156], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.7415904315108683, 2.0827319857182633, 1.6299851876183307, 2.1684156956725618, 2.034287183921455, 1.1871762208139807, 0.8378792504424102, 2.120263690500659, 2.084994480629912, 2.9692888584927264, 2.568068026384678, 3.3961089796928734, 1.6861985553023315, 1.6169479456019378, 2.9358076165138716, 2.060904295068748, 2.5509943409013407, 2.131628091545949, 3.901147327508124, 2.9432717742817194], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8409257387607284, 0.7905336961003674, 0.8127499235659481, 0.8112433294230027, 0.7583144864163893, 0.8291390931249746, 0.8013403968280814, 0.8541612432933922, 0.8189454991321705, 0.8382737451549787, 0.8623208703078673, 0.9205030742504243, 0.7910929085761658, 0.8281466327274405, 0.8835809901756569, 0.8443297960549047, 1.2717877319415767, 0.8399160173791669, 0.9004598908521413, 0.890049147265713], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8352504988448839, 0.8075514445666199, 0.8018497288930967, 0.8180859411319361, 0.7858162193716672, 0.825355382169537, 0.8320887772652218, 0.8297840877398698, 0.8057868982977172, 0.8360106869018398, 0.8498302774140614, 0.928104864138183, 0.785436378100494, 0.8023939574215003, 0.8380993659545801, 0.8419611617081771, 0.853419003800327, 0.8023814885821496, 0.8569212276662613, 0.8628890146622209], \'MLPClassifier(max_iter=2000, random_state=13)\': [3.899288683609625, 1.1952711466510968, 0.8127080148708664, 1.4165129299196408, 3.6294137987260413, 1.5697229397332986, 2.178692745130151, 1.0855984019775269, 1.0637159761211787, 1.4882963560344693, 3.9991321845398744, 3.172856214587832, 3.1026823684323164, 1.5832844479730452, 2.7699543534243283, 1.6349315659062686, 4.261371441528349, 1.057882692591494, 5.025530232686576, 2.2936025140092506], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.571979103626552, 1.1579023544935871, 0.7266321672111486, 1.2386258991677872, 1.0665069586788938, 1.1829757419292921, 1.0967268191067845, 1.0097551832487281, 1.0968495436453136, 1.23795505565115, 1.0757165333790264, 2.0738835381150866, 1.1947115343654282, 1.3971993027391338, 1.0821054752269617, 1.112378142811313, 1.1314183229932873, 1.0625299238234607, 1.183440127187299, 1.4864169054699847], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.2767478871392526, 1.7387121374168648, 0.7388531418378783, 2.808045411798095, 0.8196427651738626, 1.2099414890250666, 1.5451885235570075, 2.3561154227343155, 1.1464630198189465, 4.374513010964243, 1.1619282357521992, 2.9613176904244365, 1.0233624072153291, 2.6532256169711537, 0.8592659657170196, 1.3921416839642267, 1.1544698641149629, 0.89907927899795, 1.400217511594901, 1.6661297642189905], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.877269324526716, 0.911543387707164, 0.7170266333562096, 0.7959949600076083, 0.8212383895520179, 0.9568212222116494, 0.9120335428826772, 0.8880589645792037, 0.9160038787867006, 0.8975585415771341, 0.8631024526214519, 1.1103071633635768, 0.7798283280936563, 0.9615528062134103, 0.856460005768312, 0.978976248479039, 0.9276451450950225, 0.8061413669920808, 1.04771364322835, 0.8507560005686696], \'SVC(C=1, random_state=13)\': [0.9790718960090259, 0.9863230924001973, 0.8948855371744531, 1.0115656370287647, 0.8920112354288392, 1.0031858904626927, 1.0098811902791098, 0.9352235958355198, 0.9834984673779, 0.9261161829043679, 0.967071588935616, 1.151151634870844, 0.937115937464174, 0.9820224751983494, 0.9326784098896314, 1.0677035051717283, 1.0241981495694994, 0.9500938048423175, 1.0123477275035164, 0.9569430797540597], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8670762720473927, 0.9050324802943693, 0.7342510650219977, 0.8118539078598631, 0.8253718536620325, 1.046846296966726, 0.8477118118513157, 0.9085336196089959, 0.8801484754558283, 0.8437338796338957, 0.8840490483887017, 1.2128386423805066, 0.7795515833382359, 1.0129918323210159, 0.8705314561731037, 0.9858091237297563, 0.9478283050006507, 0.802929174492945, 1.0263338074311235, 0.8602802946034461], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.129434755925718, 12.459534504880002, 16.01940150627429, 12.459534504880002, 17.354351631797147, 12.90451788005429, 13.79448463040286, 14.239468005577146, 10.234617629008575, 14.239468005577146, 12.459534504880002, 16.01940150627429, 11.569567754531432, 12.014551129705717, 11.569567754531432, 14.239468005577146, 12.90451788005429, 12.90451788005429, 15.574418131100005, 14.684451380751435], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.015531047552891, 6.94618021782096, 4.064777764177141, 6.947634329372274, 6.6040526105491155, 8.299699200094144, 5.260545112426754, 6.162620865898926, 6.5604550434217455, 5.291222972300679, 6.114017556696146, 7.486105395719651, 5.3133434595750995, 4.857705192828526, 5.277659857625764, 7.040478613123897, 6.579023900172068, 6.162620865898925, 5.76688420734889, 7.4082783381942585], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.817814178357569, 4.073674235349254, 1.9753472364570295, 5.27809450647114, 4.5034054018440655, 4.10724638606186, 3.202626952547573, 4.083450737046828, 4.472962524423386, 3.2440314504293934, 4.931873557333099, 5.829543094243623, 3.220164054978754, 3.634061145310891, 3.6095364101748344, 4.9267283830772115, 4.521916444422732, 2.4157710306252373, 4.542347837692593, 4.895614233707167], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.4642621221719145, 3.4168331695876395, 2.054614560342437, 2.5645463455043442, 2.1069499919654664, 1.612128662533046, 2.0417036423913935, 2.061019421989538, 1.6541626355723886, 2.4187558158477866, 2.9702534284895252, 2.0862206591091543, 3.7588619029721517, 3.8751245989130436, 1.6534693791328425, 2.1340351615996225, 2.5174963444665006, 2.226066420451891, 1.6026080455080889, 2.148658396544104], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.7829724032334423, 0.8885808245422426, 0.8008761704598728, 0.8460677134762489, 0.8402800623206645, 0.8421768915918997, 0.7956575633482494, 0.8314528928339202, 0.8076309767098484, 0.8233580315757267, 0.8218442623064863, 0.8217317253126567, 0.8555682610072958, 0.8982964334798781, 0.8845318445394302, 0.8334950840402764, 1.2722668159207553, 0.9380582934507296, 0.8026371151055992, 0.80145923421563], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.7890809492772498, 0.8431862759012282, 0.7786623318853599, 0.8314554638947819, 0.8183627216068459, 0.8229217828030547, 0.8046236766470034, 0.8082755213844883, 0.8520160006558293, 0.7797492002310678, 0.8200452117750456, 0.8045262411163346, 0.8591389630531954, 0.8528920264901996, 0.8727111375162356, 0.8221954856185202, 0.8699412279991674, 0.9068523465055806, 0.7951787596623865, 0.7954050092003367], \'MLPClassifier(max_iter=2000, random_state=13)\': [1.4173380516677172, 1.2401472775025961, 3.9468755070592088, 4.924125293122849, 1.3032039564995224, 2.223351566099048, 2.0270738923673273, 5.153101812856375, 1.7655716018513885, 4.043156681474047, 1.9847971903654025, 5.792550129484428, 2.107357386187955, 1.4835566587163125, 3.794124481030498, 3.977859844960692, 3.583473037887067, 1.4140993622474858, 0.9861193950138174, 1.890364160314408], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.0881766388872798, 1.0613018081663332, 1.8959843381906827, 1.1674731756029901, 1.0006106606970464, 1.6560719800795627, 0.9690489494885874, 1.1264068008668302, 1.3178406621104735, 2.0732701272293688, 2.1887640253643696, 0.9940493862006979, 1.29007418268852, 1.4713938364473893, 1.3400028982652004, 0.7859500013134934, 1.4638002243243502, 2.8217324132410617, 0.7720313801061406, 3.758401871777707], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.232458860696727, 1.1137829830164656, 1.3983948839862697, 2.07430505253202, 1.2341153091100359, 1.4587656097005757, 0.8808002184412075, 1.3090607994467773, 2.026840804547545, 2.545135751024429, 1.2741252400929914, 2.4808894834741304, 1.09403671778572, 1.95824373294903, 1.7595690861842739, 0.8098795928806276, 3.1743141800023733, 1.5258094961540805, 0.7647616515535546, 1.0390729341006752], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.786294771755305, 0.8757336828235461, 0.8231207144056522, 0.898623827473039, 0.8265871479334694, 0.9391000013453602, 0.8019746322266487, 0.7980847096042275, 0.926653229522098, 0.8372949005361771, 0.8981004995778163, 0.8237924631405894, 0.9240657896458017, 0.9351015583980101, 0.8973249983180956, 0.8756187121778817, 0.9935948238826192, 1.0531485641301763, 0.7837698154888518, 0.7725160438705067], \'SVC(C=1, random_state=13)\': [0.9149405712159588, 1.087078116301777, 0.9016490189176879, 0.9700891292533992, 0.9541522870433153, 0.9916093326845359, 0.9152901842340577, 0.9435266486627216, 0.9916617981259044, 0.9771248771737477, 1.002763135047351, 0.9103629719524257, 0.9601848971298437, 1.1313704819975627, 0.9661170327872649, 0.9172217116561105, 1.0454455987082987, 1.0879430095639775, 0.9026789214874809, 0.9553382010750643], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8015333452740614, 0.9215216188857542, 0.8334215865392376, 0.8709202280725843, 0.8235333329549961, 0.9898938804228172, 0.7767001440537972, 0.8090913665862641, 0.96668556427982, 0.8809299622390101, 0.8704211450877578, 0.8600215968921356, 0.9563347579817648, 0.9621388793521121, 0.9066316445139629, 0.871601520516871, 0.9939102122801116, 1.0536470450933981, 0.7595922071545581, 0.7713234225863582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [12.90451788005429, 12.459534504880004, 12.459534504880002, 11.569567754531432, 16.01940150627429, 12.459534504880004, 12.90451788005429, 14.23946800557715, 13.349501255228573, 13.794484630402863, 16.019401506274292, 17.799335006971432, 16.464384881448574, 13.79448463040286, 15.574418131100003, 16.01940150627429, 15.129434755925718, 15.129434755925718, 12.459534504880004, 13.349501255228576], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.764786688376109, 6.62326487472091, 6.152609381748107, 6.189747095248756, 6.68752881757139, 7.391163592995246, 5.254085258800029, 6.606150129521898, 6.678971444971883, 5.676948146699896, 8.74403916784696, 5.3097918290510036, 6.1811897226492505, 7.41473819182098, 6.614707502121403, 6.150511862775325, 7.891853538420506, 8.294693458018733, 6.54188618667142, 7.0369269825998], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.6620997748699344, 3.2593414732805273, 3.602140352501737, 2.385539331820644, 3.7132328318508825, 4.448240542935193, 2.715360689616749, 3.221560352358409, 4.581678620438791, 4.018975615580263, 6.229181994114317, 3.6072855267576256, 3.679142773633339, 4.969361881630313, 5.357419557455558, 4.069383647130922, 5.3364603851075465, 6.244141406168887, 2.7922376108318203, 2.7914847208736355], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9530683288492852, 2.5592589168759408, 2.5335127318723085, 3.328049957288942, 3.403420597165115, 0.9101965906514035, 2.542433823383507, 1.1832987861755375, 1.742904286732884, 1.7270902886407602, 3.8088041968054562, 0.8251627566514672, 2.0570188082040732, 1.337738915089803, 2.932688214795159, 2.0661836714709194, 2.9424889346797714, 2.5852816454710212, 3.0279563230564386, 2.524322237774425], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8139193241915298, 0.8712726675882945, 0.8507464872422347, 0.8707355434797359, 0.9053793537905441, 0.8006330917130102, 0.8566182571039322, 0.7378108165450025, 0.827017365006512, 0.8741439404100725, 0.9278465366581496, 0.8100357249391655, 0.796476595325596, 0.8155039816090677, 0.8705612137755855, 0.7971778123152822, 0.8286154778995651, 0.8679709796040312, 0.8708055157714627, 0.8565099857745954], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.797346263635789, 0.8287481309488827, 0.844346598652978, 0.8303775675656939, 0.8667182862653687, 0.796219866337653, 0.8553318795825722, 0.7336387031904134, 0.8074964615674314, 0.8719718448501178, 0.8754845089184465, 0.7973896146522763, 0.7817597357275765, 0.8054903933179538, 0.8343341357103606, 0.793006791739029, 0.8265431098090641, 0.8341420414374989, 0.8544008990389963, 0.8435314641961802], \'MLPClassifier(max_iter=2000, random_state=13)\': [1.5194699298220637, 4.362775836297933, 1.4147842534906325, 1.4246710914937801, 1.8920223384631327, 1.1074164755742917, 3.012536816775623, 0.8841167401828036, 1.2738572866082425, 1.418037765532445, 1.4620644863439463, 2.189769606617473, 2.6866384206696865, 2.2972154188458194, 3.0508416422738405, 1.4888274315023475, 2.288532327138294, 1.4175430694623306, 3.635804943615935, 3.0424227830629813], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.4157897908879737, 0.9922277110502538, 1.3175459086645773, 1.2982902924330255, 1.7606293508074708, 0.9980147675128419, 1.49972037486072, 0.715021474684177, 1.3172569831491163, 1.2391739874835683, 1.1945535271448282, 1.7571286833094237, 1.0351971931194557, 0.9270226088742838, 0.8100470521959058, 1.17436742530927, 1.2945719220656144, 1.7140008793007349, 1.1207807106233378, 1.3744997360003657], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.4784018220360462, 1.2657821809249996, 1.7651214946908758, 1.5465799757170384, 1.7872617810538496, 1.0351984358167086, 1.3199043277439142, 3.2345952063512673, 3.6722135650664596, 1.6903180571336895, 1.9152823705570208, 1.2204855551806786, 1.1490911495284724, 1.430712885625709, 0.8176218690591687, 2.4723952262288753, 2.5859748506414304, 2.035119467793976, 1.0358752624627345, 2.6882470073985787], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8645477572542046, 0.942120864939774, 0.9718490317212753, 0.9561211850055281, 0.9080010240416316, 0.8586027413280516, 0.9563610621641782, 0.7758872948709116, 0.9403610244300307, 1.0674440644835692, 1.0006721119535953, 0.9361465661183189, 0.7604645767549416, 0.8751079829422356, 0.8150988920043635, 0.8547963425077801, 0.9293291138884271, 0.935550094599592, 1.0492816023218186, 0.9361905831903022], \'SVC(C=1, random_state=13)\': [1.00792230676438, 0.9662607315379109, 1.022227839772934, 0.9883110911036349, 1.0612573507015834, 0.9407362863460674, 1.0228333471135866, 0.8413984031432271, 0.9541360240268342, 1.0342761058673855, 1.0400402540362808, 0.9892142651406289, 0.8900160411108704, 1.0459123077663628, 0.9453917381601482, 0.9758341053205956, 0.9806271055035344, 0.9585272997473192, 1.1329724824546785, 0.940564739184699], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8613022814404812, 0.9771075607097387, 1.0210798909639216, 0.9538147691952429, 0.9193359216055083, 0.8714531805918212, 0.9292127596558232, 0.7798868719848115, 0.9882736981229264, 1.071395893354953, 1.041374549601939, 0.9515383415467922, 0.749701316348915, 0.913257322687392, 0.8144319179678566, 0.8510008188252925, 0.915394726545515, 0.9049817316538287, 1.0235434027806918, 0.9103192496838312], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751431, 12.459534504880002, 12.014551129705717, 15.574418131100005, 11.569567754531434, 14.239468005577146, 13.349501255228573, 9.344650878660001, 18.689301757320003, 13.794484630402863, 13.794484630402863, 14.684451380751431, 13.349501255228576, 12.459534504880002, 14.239468005577146, 14.239468005577146, 14.23946800557715, 13.79448463040286, 16.464384881448574, 13.79448463040286], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [7.507582475572603, 7.8768363121942775, 6.1169257797987715, 6.152609381748108, 6.086891327346316, 5.775441579948396, 8.301153311645457, 4.761309278552807, 6.736132126774169, 5.323998351147387, 6.151155270196794, 8.316170537871685, 4.488451356206849, 6.536880444596011, 7.460433277921135, 6.078333954746809, 5.707626006573822, 5.727648974875459, 8.34038854411889, 6.115471668247459], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.957041699890626, 5.783848008143468, 5.344374350285582, 4.5049411314042, 4.444477733795011, 4.5308383600827495, 6.645973375285134, 2.7291349829077496, 4.967322176829189, 4.088398664950578, 4.519233332200138, 5.768537985292334, 2.370440487585596, 6.59963488176351, 4.522713216288628, 5.269397701691156, 4.074753932266844, 2.7936777901191854, 4.965306275865226, 4.511247620586495], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.1246427796105842, 2.0794754725885807, 3.3754513932721686, 1.2251685203521843, 2.50775252753208, 3.358593527943935, 3.370544023661564, 1.13802041292348, 2.053462034718431, 1.6973075730975344, 1.6458598220741512, 1.2552655155879662, 2.0923406892849328, 1.2565252029791794, 2.510497100267188, 2.0911308509117967, 1.6260335987021222, 1.2254892685776346, 1.271399852106601, 3.332007190589224], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8735290238884338, 0.7885178939529847, 0.8874561178883839, 0.7757053195220222, 0.8579098384094653, 0.8598935411442163, 0.8902299658599374, 0.72732306906564, 0.8129984980366571, 0.7997536717241078, 0.8140306716466253, 0.8211409730590876, 0.8560461612284967, 0.7705042813778309, 0.8236724470930449, 0.8517421124381039, 0.796616981695267, 0.7365521355219792, 0.850530949811948, 0.8400813226079797], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8682199221293679, 0.7900965099381356, 0.8795603669001859, 0.7747760458034509, 0.8421404633101152, 0.8283875618805703, 0.8722937733059486, 0.7503239746989663, 0.8150394182032713, 0.7904396778744642, 0.8161643139810885, 0.8083340872150674, 0.8504113742421288, 0.7569159504841788, 0.8023079107174439, 0.810073395179143, 0.7993962252825095, 0.7500011762885688, 0.8054614606176621, 0.8143124832380814], \'MLPClassifier(max_iter=2000, random_state=13)\': [1.4320842495064132, 3.774820409931702, 1.6518262916374835, 1.3780032065574872, 1.9247349981266273, 1.5059326685928953, 1.2898415932377627, 0.9554792236341606, 4.398360027452612, 0.8745942513143142, 1.0962749402820273, 1.412312416205319, 1.6766067164054879, 3.3038088309901514, 1.860265592550739, 1.4812296992449148, 0.9828318375281698, 1.6286165788226201, 1.1172165726088692, 1.2133680316292905], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.3911471117911411, 0.6909000504249458, 1.4035569969899675, 0.9828499305464266, 1.2123377559653163, 1.3013350344657264, 1.5036270504857132, 2.9065154948617438, 2.8601057231831173, 0.8519526781883451, 1.6379556249963452, 1.5177046501720861, 1.1190951779840357, 0.7936950133525952, 1.152823581249989, 1.5756287364600838, 0.9662087666731708, 0.8272864263769351, 1.1370798211172894, 0.9141505538437377], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.1523897549613376, 1.8123491031638017, 1.6579781599219567, 1.0524858867909184, 2.885192116056257, 2.3577888582479933, 1.2060358482204308, 2.7934608553639992, 2.6870062676508026, 0.9205128332897808, 0.9445077768380867, 1.438813647192469, 3.928372857509216, 3.465677804794752, 3.1705413084446654, 2.040890312899795, 4.274403903837065, 1.0919266162366053, 1.004970617774472, 2.680481759416686], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.9271367521332247, 0.691037978679481, 0.9928905406599774, 0.9076804073650345, 0.9268753220964, 1.0400827594412279, 0.9358154465758247, 0.711211286988165, 0.83974987285862, 0.7877382890927568, 0.8055225188421017, 0.9261467182899279, 0.8322076344339467, 0.7742512708657742, 0.9507653260181183, 0.8784108581853978, 0.7726613752768146, 0.7794764320363736, 0.8086752358363104, 0.8198991459955073], \'SVC(C=1, random_state=13)\': [1.071626377019734, 0.8606277933788473, 1.0105002468120754, 0.9190089091610663, 0.9297588497967462, 1.0321139049874215, 1.0314186355622323, 0.8470161796733803, 0.9677314137274303, 0.9215570459371374, 0.93345773324161, 0.9078161659008979, 0.9148584577452302, 0.9014092142339187, 0.933986619919063, 0.9560598984856253, 0.9184942678850548, 0.8514375438220223, 0.9839749472794594, 0.9009475846890418], "SVC(C=1, kernel=\'poly\', random_state=13)": [1.022639931073491, 0.7035059168498247, 0.956856147811535, 0.9268664889340684, 0.9156562401232231, 0.9852404292201942, 0.9163101791415172, 0.758389149126282, 0.8509933181204953, 0.7969363123731592, 0.7991891526288687, 0.9244157666568373, 0.8709416998867967, 0.7769771832997714, 0.9421327384712623, 0.8509021128320253, 0.7850496725995102, 0.7684856405800299, 0.8816292495324195, 0.840192441581651], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751431, 8.899667503485716, 16.909368256622862, 16.909368256622862, 14.239468005577146, 14.684451380751431, 16.01940150627429, 11.124584379357145, 13.79448463040286, 11.124584379357145, 12.014551129705719, 13.79448463040286, 12.014551129705717, 12.459534504880004, 13.349501255228576, 12.90451788005429, 12.459534504880002, 13.79448463040286, 14.684451380751431, 13.349501255228576], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [7.499025102973096, 5.1791664243772635, 7.0646966193711, 6.559811636000275, 7.0068925301473435, 4.927618285175883, 5.763332576824795, 4.8848314221783555, 7.819032222970521, 6.624075578850755, 5.273464819680199, 6.558357524448961, 6.937622845221456, 3.6469206183526857, 4.42983656285325, 5.751223573701194, 5.274108227101668, 6.10982251875058, 6.658948476670244, 7.382606220395742], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [6.233237599879405, 3.1536631609750145, 5.325791561271309, 4.498553024213083, 5.344432164457241, 3.2694107716030048, 4.9346284159913, 4.077341494216669, 4.883437544838693, 3.7003131245974363, 2.7580520023415094, 5.2964283807682175, 4.4140110525371705, 1.5566793865027293, 2.423167088298335, 5.360596773345929, 4.0721245735251745, 3.5778505998189267, 4.130082027193357, 4.922519412867699], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.52707195347108, 2.027992306233598, 2.0921382999712494, 3.826475087033043, 2.1121640904649244, 2.9884195046557003, 3.8399832097283366, 2.5361137246635534, 1.3842857650354752, 1.6520204105430751, 2.9071340461094697, 1.2602469524036872, 1.3260933289140466, 2.4707630355143113, 1.5122794901980368, 1.8050464924235403, 1.7462395956793486, 3.749658300759141, 1.6408461148451587, 1.2424776897112955], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8596949218252029, 0.8369302588992195, 0.8067637350430865, 0.894507076309016, 0.8769125923069013, 0.8523650366239738, 0.9211091169186634, 0.8929527238772014, 0.860604908909654, 0.8416787597332093, 0.8195506532368403, 0.7961871426053247, 0.8609529196839952, 0.7658532500161485, 0.7627433489908344, 0.8556757612359891, 1.2200837297852472, 0.7950323112340134, 0.8333410704460817, 0.8204558166274252], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8250007060331693, 0.830349221807965, 0.7898089645783153, 0.8545578183186651, 0.8836734178060891, 0.8490292131527075, 0.8999527192768132, 0.8857966661704727, 0.8523114105662493, 0.8238370348665792, 0.8265113064105856, 0.7750203401745865, 0.8432222471799706, 0.7702486622361369, 0.7688804340115573, 0.8548894293878938, 0.8188668452734594, 0.8054066810678638, 0.8057966708465584, 0.8186710685389051], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.882438836213467, 1.4820147513460928, 1.2179038264742352, 1.06424849539806, 1.3064716819419586, 1.205600143866732, 3.3782770456108255, 1.1943796158226099, 2.3806260495207314, 1.1643071632295623, 1.4636918573413766, 1.4208022068687813, 1.4973462372157718, 2.0353977138707067, 2.7656847066620127, 1.3105104374801757, 2.489940324159525, 1.227762930685032, 2.001242495033579, 0.9941831630601126], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.1151311038721425, 1.5128651448329105, 2.057224187925083, 1.2009041387801653, 1.1866065754941157, 1.006247368694396, 1.2975321630394956, 1.2639881159531388, 1.0846974105675937, 0.8784713782069589, 1.1655237504700418, 0.856995386549768, 0.9362442663203838, 1.110406019388214, 0.8006257945134856, 1.1670332848462772, 0.9970444965924983, 0.9386865995698987, 1.4074435945986332, 1.1740952977923547], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.4371999969801952, 3.6429292740430492, 2.025927538581578, 1.2145499643072522, 1.3990449059383843, 0.994151894483075, 2.626946973251151, 2.433166818876066, 1.0186659947132632, 1.769275957264649, 1.2761671868470998, 1.2541518471786888, 1.3637092783299174, 1.1239714581344893, 1.0671502826334396, 1.3875885475137986, 1.0600974096872677, 2.2011087208014435, 1.5483754543617778, 0.8416894068404377], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8884452505420403, 0.8234732838521245, 0.8141287437350828, 0.9763205233719738, 0.8885285385262884, 0.9018482405040298, 1.0290418243989379, 0.985779077949992, 0.843453078363943, 0.9294094789618732, 0.918102762918857, 0.8071049723950621, 0.928167624817176, 0.891055348368475, 0.7732438520979876, 1.0117686993087394, 0.8265299682640966, 0.8604096391214605, 0.8722142448435278, 0.8016422193006256], \'SVC(C=1, random_state=13)\': [0.9488115709041645, 1.0898991369644198, 0.9590191805128369, 1.0033480961944354, 1.0140983776239143, 1.0367241125228033, 1.0590207197713102, 1.0079778959758383, 0.9929475995326538, 1.0384607082374202, 0.9485496194610622, 1.0232804696123696, 0.9994485607423254, 0.9811811457128748, 0.9445386596467275, 1.070535720117628, 0.9741609801464015, 1.014348355032505, 0.9913136919973087, 0.9838527199919854], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9222535691823563, 0.8854612502935924, 0.812706094523894, 0.9620639921842344, 0.8654739756887827, 0.911708673578104, 1.0478156316288336, 1.0350998125922015, 0.8586310633743351, 0.8575933029771339, 0.9217192345052102, 0.8332403222093299, 0.8958053479867893, 0.9445940087474196, 0.7691036698673323, 1.0154640897830471, 0.8391761480074511, 0.8830889985000077, 0.8974720944956943, 0.7804522646710089], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751435, 12.90451788005429, 16.909368256622862, 12.90451788005429, 14.684451380751431, 13.794484630402863, 12.90451788005429, 13.794484630402863, 16.464384881448577, 13.794484630402863, 14.684451380751431, 14.23946800557715, 10.67960100418286, 14.684451380751435, 13.794484630402863, 13.794484630402863, 15.129434755925718, 15.574418131100005, 14.239468005577146, 12.90451788005429], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.010525305477481, 6.959743332495877, 6.226241401327935, 6.959743332495877, 5.742666201101688, 6.574828862226504, 8.286136085419228, 5.71763749072464, 7.9225313982944305, 6.582575530696165, 7.82968711454281, 5.359038545675254, 5.71763749072464, 7.43476116012262, 6.106914295647953, 7.921887990872962, 6.1390462670731925, 10.043949098841951, 6.118379891350085, 4.794084657399516], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.8255747790911787, 4.464207905471744, 2.8461017226338075, 4.847331585657187, 3.635419706589437, 3.2120528434485798, 5.805675698792983, 3.2388723439095575, 4.5364875095796275, 4.932319718402431, 6.172198480593618, 3.3055983487933305, 3.261285627808882, 3.613241405143357, 3.6230277784141425, 4.965152911420798, 4.922154869807185, 5.808569989631661, 4.068361764384993, 3.140920622003156]}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.7415904315108683, 2.0827319857182633, 1.6299851876183307, 2.1684156956725618, 2.034287183921455, 1.1871762208139807, 0.8378792504424102, 2.120263690500659, 2.084994480629912, 2.9692888584927264, 2.568068026384678, 3.3961089796928734, 1.6861985553023315, 1.6169479456019378, 2.9358076165138716, 2.060904295068748, 2.5509943409013407, 2.131628091545949, 3.901147327508124, 2.9432717742817194], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8409257387607284, 0.7905336961003674, 0.8127499235659481, 0.8112433294230027, 0.7583144864163893, 0.8291390931249746, 0.8013403968280814, 0.8541612432933922, 0.8189454991321705, 0.8382737451549787, 0.8623208703078673, 0.9205030742504243, 0.7910929085761658, 0.8281466327274405, 0.8835809901756569, 0.8443297960549047, 1.2717877319415767, 0.8399160173791669, 0.9004598908521413, 0.890049147265713], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8352504988448839, 0.8075514445666199, 0.8018497288930967, 0.8180859411319361, 0.7858162193716672, 0.825355382169537, 0.8320887772652218, 0.8297840877398698, 0.8057868982977172, 0.8360106869018398, 0.8498302774140614, 0.928104864138183, 0.785436378100494, 0.8023939574215003, 0.8380993659545801, 0.8419611617081771, 0.853419003800327, 0.8023814885821496, 0.8569212276662613, 0.8628890146622209], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [3.899288683609625, 1.1952711466510968, 0.8127080148708664, 1.4165129299196408, 3.6294137987260413, 1.5697229397332986, 2.178692745130151, 1.0855984019775269, 1.0637159761211787, 1.4882963560344693, 3.9991321845398744, 3.172856214587832, 3.1026823684323164, 1.5832844479730452, 2.7699543534243283, 1.6349315659062686, 4.261371441528349, 1.057882692591494, 5.025530232686576, 2.2936025140092506], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.571979103626552, 1.1579023544935871, 0.7266321672111486, 1.2386258991677872, 1.0665069586788938, 1.1829757419292921, 1.0967268191067845, 1.0097551832487281, 1.0968495436453136, 1.23795505565115, 1.0757165333790264, 2.0738835381150866, 1.1947115343654282, 1.3971993027391338, 1.0821054752269617, 1.112378142811313, 1.1314183229932873, 1.0625299238234607, 1.183440127187299, 1.4864169054699847], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.2767478871392526, 1.7387121374168648, 0.7388531418378783, 2.808045411798095, 0.8196427651738626, 1.2099414890250666, 1.5451885235570075, 2.3561154227343155, 1.1464630198189465, 4.374513010964243, 1.1619282357521992, 2.9613176904244365, 1.0233624072153291, 2.6532256169711537, 0.8592659657170196, 1.3921416839642267, 1.1544698641149629, 0.89907927899795, 1.400217511594901, 1.6661297642189905], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.877269324526716, 0.911543387707164, 0.7170266333562096, 0.7959949600076083, 0.8212383895520179, 0.9568212222116494, 0.9120335428826772, 0.8880589645792037, 0.9160038787867006, 0.8975585415771341, 0.8631024526214519, 1.1103071633635768, 0.7798283280936563, 0.9615528062134103, 0.856460005768312, 0.978976248479039, 0.9276451450950225, 0.8061413669920808, 1.04771364322835, 0.8507560005686696], \'SVC(C=1, random_state=13)\': [0.9790718960090259, 0.9863230924001973, 0.8948855371744531, 1.0115656370287647, 0.8920112354288392, 1.0031858904626927, 1.0098811902791098, 0.9352235958355198, 0.9834984673779, 0.9261161829043679, 0.967071588935616, 1.151151634870844, 0.937115937464174, 0.9820224751983494, 0.9326784098896314, 1.0677035051717283, 1.0241981495694994, 0.9500938048423175, 1.0123477275035164, 0.9569430797540597], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8670762720473927, 0.9050324802943693, 0.7342510650219977, 0.8118539078598631, 0.8253718536620325, 1.046846296966726, 0.8477118118513157, 0.9085336196089959, 0.8801484754558283, 0.8437338796338957, 0.8840490483887017, 1.2128386423805066, 0.7795515833382359, 1.0129918323210159, 0.8705314561731037, 0.9858091237297563, 0.9478283050006507, 0.802929174492945, 1.0263338074311235, 0.8602802946034461], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.129434755925718, 12.459534504880002, 16.01940150627429, 12.459534504880002, 17.354351631797147, 12.90451788005429, 13.79448463040286, 14.239468005577146, 10.234617629008575, 14.239468005577146, 12.459534504880002, 16.01940150627429, 11.569567754531432, 12.014551129705717, 11.569567754531432, 14.239468005577146, 12.90451788005429, 12.90451788005429, 15.574418131100005, 14.684451380751435], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.015531047552891, 6.94618021782096, 4.064777764177141, 6.947634329372274, 6.6040526105491155, 8.299699200094144, 5.260545112426754, 6.162620865898926, 6.5604550434217455, 5.291222972300679, 6.114017556696146, 7.486105395719651, 5.3133434595750995, 4.857705192828526, 5.277659857625764, 7.040478613123897, 6.579023900172068, 6.162620865898925, 5.76688420734889, 7.4082783381942585], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.817814178357569, 4.073674235349254, 1.9753472364570295, 5.27809450647114, 4.5034054018440655, 4.10724638606186, 3.202626952547573, 4.083450737046828, 4.472962524423386, 3.2440314504293934, 4.931873557333099, 5.829543094243623, 3.220164054978754, 3.634061145310891, 3.6095364101748344, 4.9267283830772115, 4.521916444422732, 2.4157710306252373, 4.542347837692593, 4.895614233707167]}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.4642621221719145, 3.4168331695876395, 2.054614560342437, 2.5645463455043442, 2.1069499919654664, 1.612128662533046, 2.0417036423913935, 2.061019421989538, 1.6541626355723886, 2.4187558158477866, 2.9702534284895252, 2.0862206591091543, 3.7588619029721517, 3.8751245989130436, 1.6534693791328425, 2.1340351615996225, 2.5174963444665006, 2.226066420451891, 1.6026080455080889, 2.148658396544104], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.7829724032334423, 0.8885808245422426, 0.8008761704598728, 0.8460677134762489, 0.8402800623206645, 0.8421768915918997, 0.7956575633482494, 0.8314528928339202, 0.8076309767098484, 0.8233580315757267, 0.8218442623064863, 0.8217317253126567, 0.8555682610072958, 0.8982964334798781, 0.8845318445394302, 0.8334950840402764, 1.2722668159207553, 0.9380582934507296, 0.8026371151055992, 0.80145923421563], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.7890809492772498, 0.8431862759012282, 0.7786623318853599, 0.8314554638947819, 0.8183627216068459, 0.8229217828030547, 0.8046236766470034, 0.8082755213844883, 0.8520160006558293, 0.7797492002310678, 0.8200452117750456, 0.8045262411163346, 0.8591389630531954, 0.8528920264901996, 0.8727111375162356, 0.8221954856185202, 0.8699412279991674, 0.9068523465055806, 0.7951787596623865, 0.7954050092003367], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [1.4173380516677172, 1.2401472775025961, 3.9468755070592088, 4.924125293122849, 1.3032039564995224, 2.223351566099048, 2.0270738923673273, 5.153101812856375, 1.7655716018513885, 4.043156681474047, 1.9847971903654025, 5.792550129484428, 2.107357386187955, 1.4835566587163125, 3.794124481030498, 3.977859844960692, 3.583473037887067, 1.4140993622474858, 0.9861193950138174, 1.890364160314408], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.0881766388872798, 1.0613018081663332, 1.8959843381906827, 1.1674731756029901, 1.0006106606970464, 1.6560719800795627, 0.9690489494885874, 1.1264068008668302, 1.3178406621104735, 2.0732701272293688, 2.1887640253643696, 0.9940493862006979, 1.29007418268852, 1.4713938364473893, 1.3400028982652004, 0.7859500013134934, 1.4638002243243502, 2.8217324132410617, 0.7720313801061406, 3.758401871777707], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.232458860696727, 1.1137829830164656, 1.3983948839862697, 2.07430505253202, 1.2341153091100359, 1.4587656097005757, 0.8808002184412075, 1.3090607994467773, 2.026840804547545, 2.545135751024429, 1.2741252400929914, 2.4808894834741304, 1.09403671778572, 1.95824373294903, 1.7595690861842739, 0.8098795928806276, 3.1743141800023733, 1.5258094961540805, 0.7647616515535546, 1.0390729341006752], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.786294771755305, 0.8757336828235461, 0.8231207144056522, 0.898623827473039, 0.8265871479334694, 0.9391000013453602, 0.8019746322266487, 0.7980847096042275, 0.926653229522098, 0.8372949005361771, 0.8981004995778163, 0.8237924631405894, 0.9240657896458017, 0.9351015583980101, 0.8973249983180956, 0.8756187121778817, 0.9935948238826192, 1.0531485641301763, 0.7837698154888518, 0.7725160438705067], \'SVC(C=1, random_state=13)\': [0.9149405712159588, 1.087078116301777, 0.9016490189176879, 0.9700891292533992, 0.9541522870433153, 0.9916093326845359, 0.9152901842340577, 0.9435266486627216, 0.9916617981259044, 0.9771248771737477, 1.002763135047351, 0.9103629719524257, 0.9601848971298437, 1.1313704819975627, 0.9661170327872649, 0.9172217116561105, 1.0454455987082987, 1.0879430095639775, 0.9026789214874809, 0.9553382010750643], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8015333452740614, 0.9215216188857542, 0.8334215865392376, 0.8709202280725843, 0.8235333329549961, 0.9898938804228172, 0.7767001440537972, 0.8090913665862641, 0.96668556427982, 0.8809299622390101, 0.8704211450877578, 0.8600215968921356, 0.9563347579817648, 0.9621388793521121, 0.9066316445139629, 0.871601520516871, 0.9939102122801116, 1.0536470450933981, 0.7595922071545581, 0.7713234225863582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [12.90451788005429, 12.459534504880004, 12.459534504880002, 11.569567754531432, 16.01940150627429, 12.459534504880004, 12.90451788005429, 14.23946800557715, 13.349501255228573, 13.794484630402863, 16.019401506274292, 17.799335006971432, 16.464384881448574, 13.79448463040286, 15.574418131100003, 16.01940150627429, 15.129434755925718, 15.129434755925718, 12.459534504880004, 13.349501255228576], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.764786688376109, 6.62326487472091, 6.152609381748107, 6.189747095248756, 6.68752881757139, 7.391163592995246, 5.254085258800029, 6.606150129521898, 6.678971444971883, 5.676948146699896, 8.74403916784696, 5.3097918290510036, 6.1811897226492505, 7.41473819182098, 6.614707502121403, 6.150511862775325, 7.891853538420506, 8.294693458018733, 6.54188618667142, 7.0369269825998], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.6620997748699344, 3.2593414732805273, 3.602140352501737, 2.385539331820644, 3.7132328318508825, 4.448240542935193, 2.715360689616749, 3.221560352358409, 4.581678620438791, 4.018975615580263, 6.229181994114317, 3.6072855267576256, 3.679142773633339, 4.969361881630313, 5.357419557455558, 4.069383647130922, 5.3364603851075465, 6.244141406168887, 2.7922376108318203, 2.7914847208736355]}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9530683288492852, 2.5592589168759408, 2.5335127318723085, 3.328049957288942, 3.403420597165115, 0.9101965906514035, 2.542433823383507, 1.1832987861755375, 1.742904286732884, 1.7270902886407602, 3.8088041968054562, 0.8251627566514672, 2.0570188082040732, 1.337738915089803, 2.932688214795159, 2.0661836714709194, 2.9424889346797714, 2.5852816454710212, 3.0279563230564386, 2.524322237774425], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8139193241915298, 0.8712726675882945, 0.8507464872422347, 0.8707355434797359, 0.9053793537905441, 0.8006330917130102, 0.8566182571039322, 0.7378108165450025, 0.827017365006512, 0.8741439404100725, 0.9278465366581496, 0.8100357249391655, 0.796476595325596, 0.8155039816090677, 0.8705612137755855, 0.7971778123152822, 0.8286154778995651, 0.8679709796040312, 0.8708055157714627, 0.8565099857745954], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.797346263635789, 0.8287481309488827, 0.844346598652978, 0.8303775675656939, 0.8667182862653687, 0.796219866337653, 0.8553318795825722, 0.7336387031904134, 0.8074964615674314, 0.8719718448501178, 0.8754845089184465, 0.7973896146522763, 0.7817597357275765, 0.8054903933179538, 0.8343341357103606, 0.793006791739029, 0.8265431098090641, 0.8341420414374989, 0.8544008990389963, 0.8435314641961802], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [1.5194699298220637, 4.362775836297933, 1.4147842534906325, 1.4246710914937801, 1.8920223384631327, 1.1074164755742917, 3.012536816775623, 0.8841167401828036, 1.2738572866082425, 1.418037765532445, 1.4620644863439463, 2.189769606617473, 2.6866384206696865, 2.2972154188458194, 3.0508416422738405, 1.4888274315023475, 2.288532327138294, 1.4175430694623306, 3.635804943615935, 3.0424227830629813], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.4157897908879737, 0.9922277110502538, 1.3175459086645773, 1.2982902924330255, 1.7606293508074708, 0.9980147675128419, 1.49972037486072, 0.715021474684177, 1.3172569831491163, 1.2391739874835683, 1.1945535271448282, 1.7571286833094237, 1.0351971931194557, 0.9270226088742838, 0.8100470521959058, 1.17436742530927, 1.2945719220656144, 1.7140008793007349, 1.1207807106233378, 1.3744997360003657], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.4784018220360462, 1.2657821809249996, 1.7651214946908758, 1.5465799757170384, 1.7872617810538496, 1.0351984358167086, 1.3199043277439142, 3.2345952063512673, 3.6722135650664596, 1.6903180571336895, 1.9152823705570208, 1.2204855551806786, 1.1490911495284724, 1.430712885625709, 0.8176218690591687, 2.4723952262288753, 2.5859748506414304, 2.035119467793976, 1.0358752624627345, 2.6882470073985787], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8645477572542046, 0.942120864939774, 0.9718490317212753, 0.9561211850055281, 0.9080010240416316, 0.8586027413280516, 0.9563610621641782, 0.7758872948709116, 0.9403610244300307, 1.0674440644835692, 1.0006721119535953, 0.9361465661183189, 0.7604645767549416, 0.8751079829422356, 0.8150988920043635, 0.8547963425077801, 0.9293291138884271, 0.935550094599592, 1.0492816023218186, 0.9361905831903022], \'SVC(C=1, random_state=13)\': [1.00792230676438, 0.9662607315379109, 1.022227839772934, 0.9883110911036349, 1.0612573507015834, 0.9407362863460674, 1.0228333471135866, 0.8413984031432271, 0.9541360240268342, 1.0342761058673855, 1.0400402540362808, 0.9892142651406289, 0.8900160411108704, 1.0459123077663628, 0.9453917381601482, 0.9758341053205956, 0.9806271055035344, 0.9585272997473192, 1.1329724824546785, 0.940564739184699], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8613022814404812, 0.9771075607097387, 1.0210798909639216, 0.9538147691952429, 0.9193359216055083, 0.8714531805918212, 0.9292127596558232, 0.7798868719848115, 0.9882736981229264, 1.071395893354953, 1.041374549601939, 0.9515383415467922, 0.749701316348915, 0.913257322687392, 0.8144319179678566, 0.8510008188252925, 0.915394726545515, 0.9049817316538287, 1.0235434027806918, 0.9103192496838312], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751431, 12.459534504880002, 12.014551129705717, 15.574418131100005, 11.569567754531434, 14.239468005577146, 13.349501255228573, 9.344650878660001, 18.689301757320003, 13.794484630402863, 13.794484630402863, 14.684451380751431, 13.349501255228576, 12.459534504880002, 14.239468005577146, 14.239468005577146, 14.23946800557715, 13.79448463040286, 16.464384881448574, 13.79448463040286], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [7.507582475572603, 7.8768363121942775, 6.1169257797987715, 6.152609381748108, 6.086891327346316, 5.775441579948396, 8.301153311645457, 4.761309278552807, 6.736132126774169, 5.323998351147387, 6.151155270196794, 8.316170537871685, 4.488451356206849, 6.536880444596011, 7.460433277921135, 6.078333954746809, 5.707626006573822, 5.727648974875459, 8.34038854411889, 6.115471668247459], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.957041699890626, 5.783848008143468, 5.344374350285582, 4.5049411314042, 4.444477733795011, 4.5308383600827495, 6.645973375285134, 2.7291349829077496, 4.967322176829189, 4.088398664950578, 4.519233332200138, 5.768537985292334, 2.370440487585596, 6.59963488176351, 4.522713216288628, 5.269397701691156, 4.074753932266844, 2.7936777901191854, 4.965306275865226, 4.511247620586495]}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.1246427796105842, 2.0794754725885807, 3.3754513932721686, 1.2251685203521843, 2.50775252753208, 3.358593527943935, 3.370544023661564, 1.13802041292348, 2.053462034718431, 1.6973075730975344, 1.6458598220741512, 1.2552655155879662, 2.0923406892849328, 1.2565252029791794, 2.510497100267188, 2.0911308509117967, 1.6260335987021222, 1.2254892685776346, 1.271399852106601, 3.332007190589224], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8735290238884338, 0.7885178939529847, 0.8874561178883839, 0.7757053195220222, 0.8579098384094653, 0.8598935411442163, 0.8902299658599374, 0.72732306906564, 0.8129984980366571, 0.7997536717241078, 0.8140306716466253, 0.8211409730590876, 0.8560461612284967, 0.7705042813778309, 0.8236724470930449, 0.8517421124381039, 0.796616981695267, 0.7365521355219792, 0.850530949811948, 0.8400813226079797], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8682199221293679, 0.7900965099381356, 0.8795603669001859, 0.7747760458034509, 0.8421404633101152, 0.8283875618805703, 0.8722937733059486, 0.7503239746989663, 0.8150394182032713, 0.7904396778744642, 0.8161643139810885, 0.8083340872150674, 0.8504113742421288, 0.7569159504841788, 0.8023079107174439, 0.810073395179143, 0.7993962252825095, 0.7500011762885688, 0.8054614606176621, 0.8143124832380814], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [1.4320842495064132, 3.774820409931702, 1.6518262916374835, 1.3780032065574872, 1.9247349981266273, 1.5059326685928953, 1.2898415932377627, 0.9554792236341606, 4.398360027452612, 0.8745942513143142, 1.0962749402820273, 1.412312416205319, 1.6766067164054879, 3.3038088309901514, 1.860265592550739, 1.4812296992449148, 0.9828318375281698, 1.6286165788226201, 1.1172165726088692, 1.2133680316292905], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.3911471117911411, 0.6909000504249458, 1.4035569969899675, 0.9828499305464266, 1.2123377559653163, 1.3013350344657264, 1.5036270504857132, 2.9065154948617438, 2.8601057231831173, 0.8519526781883451, 1.6379556249963452, 1.5177046501720861, 1.1190951779840357, 0.7936950133525952, 1.152823581249989, 1.5756287364600838, 0.9662087666731708, 0.8272864263769351, 1.1370798211172894, 0.9141505538437377], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.1523897549613376, 1.8123491031638017, 1.6579781599219567, 1.0524858867909184, 2.885192116056257, 2.3577888582479933, 1.2060358482204308, 2.7934608553639992, 2.6870062676508026, 0.9205128332897808, 0.9445077768380867, 1.438813647192469, 3.928372857509216, 3.465677804794752, 3.1705413084446654, 2.040890312899795, 4.274403903837065, 1.0919266162366053, 1.004970617774472, 2.680481759416686], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.9271367521332247, 0.691037978679481, 0.9928905406599774, 0.9076804073650345, 0.9268753220964, 1.0400827594412279, 0.9358154465758247, 0.711211286988165, 0.83974987285862, 0.7877382890927568, 0.8055225188421017, 0.9261467182899279, 0.8322076344339467, 0.7742512708657742, 0.9507653260181183, 0.8784108581853978, 0.7726613752768146, 0.7794764320363736, 0.8086752358363104, 0.8198991459955073], \'SVC(C=1, random_state=13)\': [1.071626377019734, 0.8606277933788473, 1.0105002468120754, 0.9190089091610663, 0.9297588497967462, 1.0321139049874215, 1.0314186355622323, 0.8470161796733803, 0.9677314137274303, 0.9215570459371374, 0.93345773324161, 0.9078161659008979, 0.9148584577452302, 0.9014092142339187, 0.933986619919063, 0.9560598984856253, 0.9184942678850548, 0.8514375438220223, 0.9839749472794594, 0.9009475846890418], "SVC(C=1, kernel=\'poly\', random_state=13)": [1.022639931073491, 0.7035059168498247, 0.956856147811535, 0.9268664889340684, 0.9156562401232231, 0.9852404292201942, 0.9163101791415172, 0.758389149126282, 0.8509933181204953, 0.7969363123731592, 0.7991891526288687, 0.9244157666568373, 0.8709416998867967, 0.7769771832997714, 0.9421327384712623, 0.8509021128320253, 0.7850496725995102, 0.7684856405800299, 0.8816292495324195, 0.840192441581651], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [14.684451380751431, 8.899667503485716, 16.909368256622862, 16.909368256622862, 14.239468005577146, 14.684451380751431, 16.01940150627429, 11.124584379357145, 13.79448463040286, 11.124584379357145, 12.014551129705719, 13.79448463040286, 12.014551129705717, 12.459534504880004, 13.349501255228576, 12.90451788005429, 12.459534504880002, 13.79448463040286, 14.684451380751431, 13.349501255228576], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [7.499025102973096, 5.1791664243772635, 7.0646966193711, 6.559811636000275, 7.0068925301473435, 4.927618285175883, 5.763332576824795, 4.8848314221783555, 7.819032222970521, 6.624075578850755, 5.273464819680199, 6.558357524448961, 6.937622845221456, 3.6469206183526857, 4.42983656285325, 5.751223573701194, 5.274108227101668, 6.10982251875058, 6.658948476670244, 7.382606220395742], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [6.233237599879405, 3.1536631609750145, 5.325791561271309, 4.498553024213083, 5.344432164457241, 3.2694107716030048, 4.9346284159913, 4.077341494216669, 4.883437544838693, 3.7003131245974363, 2.7580520023415094, 5.2964283807682175, 4.4140110525371705, 1.5566793865027293, 2.423167088298335, 5.360596773345929, 4.0721245735251745, 3.5778505998189267, 4.130082027193357, 4.922519412867699]}'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+    <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f191c9aa590&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1917dbce10&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1917d9f190&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19279fe8d0&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1922d227d0&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1922d23250&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922d22fd0&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922d22d50&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922d23290&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1922d23090&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1922d22ed0&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1922d23910&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff868a31d50&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff869600d90&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ecee290&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ecebc10&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ef49c90&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff8640dba90&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff8640dbd50&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff8640db9d0&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff8640db8d0&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86a0162d0&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff8640db6d0&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff8640db510&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb028c25650&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb02e2724d0&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb02e1b9cd0&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb02e272550&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb02222fed0&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb02222f9d0&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb02222f5d0&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb02222f350&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb02222f290&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb02222f210&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb02222f190&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb02222f010&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe7100afe90&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe7100daf10&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe722195510&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe71bd0e290&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe722195f50&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe722195890&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe722196d50&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe722194ed0&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe722194f50&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe7100a9990&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe722195050&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe7221949d0&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a5375a10&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a55a1390&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd796538290&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55a0f10&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd79653ae90&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd796538090&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55a3c90&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd79653a4d0&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd796539b10&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd796539e50&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd796538310&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd796538350&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a55eb990&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a55de990&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd791be5a10&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55df010&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd79702db50&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55a8090&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd79653be90&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55a97d0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55a8cd0&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd791bcb250&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55aad90&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55a8850&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe71001e750&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe7100ffb10&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe722123950&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe7100ffd10&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe72210c690&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe72210b9d0&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe7220e6a50&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe7220e6f50&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe7220e4c50&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe722109990&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe7220e52d0&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe7100c0850&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff8640e8690&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86eceb390&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86efbf7d0&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86efa7690&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff8640d5290&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff8640f0950&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff8640f00d0&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff8640f2950&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ef91090&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff8640d73d0&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef91c50&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef905d0&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1922cb7390&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1922d35250&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1922d4ef50&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1922d363d0&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f191ce44990&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1922ad1950&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922ad0410&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922d25690&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1922d41fd0&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1917e060d0&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1917e05d90&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1917e05ad0&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb028052490&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb022253950&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb01c151250&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb01c1ae9d0&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb02dfd3cd0&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb01c0dcd50&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb01c0debd0&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb01c0dc310&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb01c0dd390&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb01c1ad0d0&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb01c0de050&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb01c0de1d0&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86efd3d10&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86f04d850&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86eebabd0&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86eecfe90&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86efc6dd0&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ed77710&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86efef850&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86f059dd0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86f0585d0&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86f04e2d0&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86f045950&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ed7f690&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2db2c290&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2d8e6310&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2d8e8e50&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2d8e7010&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1eb730d0&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2db17890&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d8d0490&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d8d3a50&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d8bfcd0&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2d8be790&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2d8be110&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1a144e50&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f040664d910&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0405b48710&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0401120d90&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04010f2c90&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04011322d0&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0405b124d0&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0405aec590&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0405aeced0&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0405aef990&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0405b112d0&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0405b09c50&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0405afca50&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a5501310&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a53c2250&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54d1f50&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53c40d0&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53f1950&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53d8190&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a53b3290&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a53b1a50&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a56a8650&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd791bcb050&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a56a84d0&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a56a8550&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db97fa290&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9da60cfb10&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db9818710&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db97df950&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9da6064710&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db97d1190&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db97fa410&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db97d0690&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db97d3010&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9da60dfa90&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9da60df910&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9da60df810&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2db7d550&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2db5ba50&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2dbba610&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2dba4650&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1a1f12d0&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1a1f21d0&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d9490d0&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d948ad0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2d948090&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2db34c90&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2d9480d0&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2d948150&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ef17710&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ece7690&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ed0d850&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ece7c90&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff8696543d0&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff868b1ab50&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed07390&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed9add0&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed9b210&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ece73d0&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ed99e50&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef1c290&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414a1fd90&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414ad7990&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414a4c590&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0414ad7710&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04011c1d90&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04011e50d0&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04011e3110&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04011e2f10&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04011ce950&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04011e12d0&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0414a324d0&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0414a62690&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9dab5ba250&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9da611d0d0&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9da6162650&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9da615f990&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9daaa0aad0&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db9aba510&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9daaaaa410&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9ab9250&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9ab93d0&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9daad77210&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9874710&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db98745d0&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f3635f01cd0&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f364b459550&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f364eaa6a90&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f364b459350&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f3635ec6490&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f3636343510&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f36363408d0&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f36366f6cd0&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f36366f5c10&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f3638609510&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f3635a00190&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f3635aeed50&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff8640f0690&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ede2950&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ef04190&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86efa2290&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86efc6f50&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86edd1e50&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86edd1490&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86edd7810&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86edd7850&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef573d0&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86edd5950&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef10650&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a557bf10&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a565d3d0&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a563b290&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53ab190&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd791c2ce50&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55a69d0&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a561d510&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a561c650&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5500ed0&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a5500490&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55010d0&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55004d0&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2f016d90&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd1f64c590&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd3473f1d0&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1eda4290&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1f9ee290&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1eae6090&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1f60c8d0&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1eabf410&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd3825fbd0&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1f1f6cd0&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1f1f64d0&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1ed681d0&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9dc067fd90&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9dabb2c990&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9daaa0aa10&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9dab565d50&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9daaa08390&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9dab53a7d0&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9dab122910&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9dab122b90&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9dab121cd0&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9daac91650&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9daac908d0&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9dbaf117d0&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f78c3c370d0&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f78aac2ac50&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f78ab8895d0&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f78ac15a8d0&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f78ab009650&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f78ab0b4990&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f78aa94cc50&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f78ab079110&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f78ab0575d0&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f78ab4bf190&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f78ab4bc810&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f78aa96c3d0&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff864168c10&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86efa0450&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ecf1c50&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86eeaf3d0&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86eecadd0&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86eecae50&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86eea7810&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86eea7690&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86eea6710&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff8641825d0&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff864180950&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86eee5950&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9dab58a250&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9daaa9fdd0&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9daaa8fd90&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9daaa94ad0&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9da6073750&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9daaab8690&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9da60cd950&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9da60b50d0&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9cd6b50&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9cd7d10&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9cd7d90&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9cd7bd0&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd791bf0810&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54d2b10&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a557ac10&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a5501310&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a54db290&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a54d7010&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55be750&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55bce50&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a54ee190&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a54e4390&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a56bbf10&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a56b8d10&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd1eb34290&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd1a139d90&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd1eb53190&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1a139590&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1eb92d10&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1f60f010&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1eb2c410&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2ddc3e10&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2ddc3c90&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2ddc3c50&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2ddc3c10&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2ddc3d50&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f041fc2a110&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f04061b1990&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f04065cb390&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f041bcbb050&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0405a81090&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0405a81850&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04061ec5d0&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0406215910&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04061ed250&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f041aa3b810&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f040612ded0&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04147b2590&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a555b290&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd791be9950&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54369d0&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55de190&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a555f010&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a555c0d0&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5574550&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55753d0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5577890&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a559aa50&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a5599090&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55995d0&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ee87dd0&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ee93c10&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ee7a150&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ee92690&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ef36210&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ed08950&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed0a950&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed08f90&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86eeaabd0&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef5e2d0&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86eea9490&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86eebf710&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc23d15d450&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc255c743d0&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc23d52db10&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc23d12c390&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc23c9159d0&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc23c5d9dd0&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23c5f2c90&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23cd41e50&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23cd05890&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23cd07790&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23c5d9ed0&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23d709bd0&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cc21279d0&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cc28ef3d0&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cc21d0810&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cc4d3fc50&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cc257e210&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cc1d0f3d0&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cc253fc90&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cc253ef10&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cc253c750&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cd76f1a90&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cc3057ad0&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cd76f1a10&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f08350cfcd0&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0835036ad0&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f08358a4110&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f083490c310&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f084a5d34d0&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f084a5d1950&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f08354d6e90&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f08354d6f10&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0835098650&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f083ab6d850&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f083ab6d8d0&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f084a5e6290&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f084e0ea150&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f08349ade10&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f083499c250&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0834980210&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f08349bc850&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f083498c990&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7f08349e1410&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7f083496b590&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7f083fc3bc50&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f083fc3a3d0&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f083fc3ba90&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f083fc3ba50&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86eed5850&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ed47950&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ed7c190&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ed47f90&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86eced290&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ed10c10&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed13d10&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ed26210&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86efe2bd0&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ed47410&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86efe3750&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86efe1f10&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a555f050&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a534f010&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a56bb290&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a534e990&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53ae190&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a53ae290&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5676190&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a557a290&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a557b910&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a534b250&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55790d0&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a557a6d0&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc237c4fdd0&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc23d462910&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fc23c662ed0&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc242b17ed0&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc237c6a990&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fc237c539d0&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23c6ae210&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23c6ad8d0&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7fc23c6adcd0&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23ccd73d0&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23c684910&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fc23c68d6d0&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cd0c74750&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cbd0d5510&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f6cc1a59a10&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cc2995410&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cd69b7810&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f6cd0d4fe50&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cd0d4fb10&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cd0d4fb90&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7f6cd0d4fad0&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cc254d250&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cd0d4fbd0&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f6cd0d4fa10&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2da8c290&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2da69950&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2d911d90&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2d924dd0&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2da9d9d0&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2d8d0e50&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1eb2c410&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2db27ed0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2db279d0&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2db27090&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2db25150&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd2db25810&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db97f73d0&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db9825f50&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db983a650&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9dab567950&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db9abc950&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db9abca90&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9abcb50&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9abca50&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9abcc10&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9abccd0&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9abcd50&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9abc350&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86eeffdd0&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ee96210&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86ef15850&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff8696543d0&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ee92dd0&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86ee92990&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ee90e50&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ee92c50&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86ef18690&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef4f710&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef4d950&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86efdf390&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f04149fa7d0&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414b6c590&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414b00d90&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0414ad9f90&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0414b2d390&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04149e9190&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0414b26b90&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0414b52d90&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0414b53b50&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04061b2210&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0414b52d10&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04011bde10&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54d3d10&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a55201d0&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54cc450&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a556d510&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a5524e50&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a5544550&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5546990&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a55311d0&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a5532f90&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55d6d50&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55d4810&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a55d7010&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db9a8a290&gt;: [1.1926394209484867, 1.7709091942009367, 1.8103756052249187, 1.7967131344628173, 2.1959006123946314, 2.741885373481709, 1.7392094388443182, 2.2347570340584078, 1.2801948606645546, 2.307324674957181, 1.6376863006142388, 1.831484296249147, 2.2489402847864906, 1.811204321765238, 1.7668549188502953, 1.3290108976718347, 2.730288955475556, 3.690165789288857, 3.7653307149751063, 0.8801697053946406], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9da60cf990&gt;: [0.8122159522637299, 0.8010090314643475, 0.8057169623825505, 0.8399962736336732, 0.7448366074960222, 0.8650809191516946, 0.796587660746347, 0.867390560998385, 0.7969975405525869, 0.885977967838235, 0.8215590890332977, 0.8627988985705497, 0.8466759654904409, 0.8524829061272859, 0.8325479611042208, 0.8135354361765131, 0.888839806900878, 0.8828588957126198, 0.8373090993294572, 0.8314909016601967], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9db9a47710&gt;: [0.799354403564963, 0.8021735543726218, 0.7773163667093791, 0.8434348842495161, 0.7533124802532389, 0.839337190254251, 0.7826703917230721, 0.8662727822423211, 0.7881977652828281, 0.8661319636643011, 0.7919599879199034, 0.8285131088827501, 0.8733290029827062, 0.828873657160886, 0.8108388269865834, 0.802942008714068, 0.8555792517745586, 0.8278106510310179, 0.8006945471589779, 0.8428094187684975], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9dc3bc2850&gt;: [1.6148993034591903, 5.6669372683255625, 1.6855374678416593, 2.1088216748951347, 2.9208789068597327, 2.1059955374307466, 4.633126232346066, 4.852034682589764, 1.6014030040340403, 1.0950793564511587, 2.0690370709186223, 1.413703353869346, 3.8410779120669503, 3.9023675978559536, 1.0107802770284755, 1.8338818554858334, 2.753431887515378, 2.99384174738883, 1.7939995865874931, 1.3416305823721189], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9da60b4910&gt;: [2.877931050460197, 1.012782347903369, 1.0178345722550366, 1.977115136868511, 1.1592304616979954, 1.4845585393609888, 1.5862503583942378, 1.2689786503362062, 1.0317635616156058, 1.4480545085857999, 3.0410457939446918, 1.3228574296713842, 1.1233292570581472, 1.5158125474712618, 1.1094144512371593, 1.011853459728802, 1.033164946246111, 1.0407740634950473, 1.424748294350457, 1.9936970869302837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9db9961190&gt;: [2.0253172747008708, 4.35128489016068, 1.072198048607407, 3.160696901010208, 1.255395915603775, 1.3203104839467177, 0.916690561225417, 1.8283220404870006, 1.1556449079964781, 1.3492971316697238, 1.9370264850671168, 1.2826569496074998, 1.0900247957997984, 1.524860771725669, 4.0485285099583495, 3.2151871579670535, 1.1153445932056851, 1.61696047898305, 2.5556108359089915, 1.9814302883073514], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9a8a410&gt;: [0.8482989546072925, 0.848800656568812, 0.7997098964381575, 1.0223494380425997, 0.818311066877254, 0.9463775011137403, 0.8395879759467915, 0.9695731400727752, 0.785953262158514, 0.8731659555454505, 0.9394992108099234, 0.8397737752865422, 0.8769795525985363, 0.9904769106136556, 0.8565766812040658, 0.7919632670409339, 0.9086056664715245, 0.861220545664979, 0.9294676346068774, 0.8801336240286269], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9825cd0&gt;: [0.8868469852041293, 0.9131974851765732, 0.8894515373983837, 0.9987898257023349, 0.8992366164787396, 0.9847182632486595, 0.9011223390303833, 0.95881731040777, 0.802672471176963, 1.0171572194632497, 0.9270176604472893, 0.9136783900661768, 0.9606499534050622, 1.0198480333649405, 0.9480427949754391, 0.8756705598680025, 0.942622875002788, 0.9308726376710337, 0.9113621442171708, 0.9655853118445918], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9db9825e50&gt;: [0.845010402174423, 0.8047274935776917, 0.8419456995634597, 1.0666013422688896, 0.8335057610842237, 0.9332362195550008, 0.8400495857971415, 0.9477794695157559, 0.782194336602939, 0.9034404886961475, 0.9460577606696418, 0.8524562933056258, 0.8609401639819217, 0.9650733340919169, 0.8496119882179498, 0.7927100985721751, 0.9116150490142149, 0.8760902290115783, 0.9398207531334636, 0.877074647245052], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9825210&gt;: [11.513944832634646, 9.51151964435036, 16.019401506274292, 13.516370020918933, 13.015763723847861, 13.015763723847861, 15.51879520920322, 13.516370020918933, 15.018188912132148, 12.014551129705717, 11.513944832634646, 13.01576372384786, 13.516370020918933, 12.515157426776788, 12.515157426776788, 13.015763723847861, 12.014551129705717, 11.513944832634646, 15.018188912132144, 13.516370020918933], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db9826150&gt;: [4.445175492790214, 6.249963962303021, 6.8808176689244664, 7.327469076491561, 3.4446867319972236, 4.8751207296497245, 5.906126498461273, 7.816088620543809, 4.442815783945834, 6.392921958221371, 5.829645769617954, 5.400612574904518, 7.799194241039304, 6.8092445665668295, 6.813240150906437, 6.8606515384295035, 5.320324470518514, 5.428769874078697, 8.256384734926916, 7.358898126656196], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9db98252d0&gt;: [4.061969899795781, 2.9759827912448915, 3.547380230413757, 5.929060603011606, 2.0561922457809825, 4.00541772550433, 3.985677379749385, 4.017182576376999, 3.00991730593708, 4.987154329151431, 3.974176884136617, 3.0718476903233296, 5.431289166671108, 4.477142890052069, 3.5266134344234477, 3.0478428366917982, 3.9579569708350895, 2.1393802518406764, 5.931420311855986, 6.463018768831809]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a54f7c10&gt;: [3.2000985785383027, 0.8382256394038675, 2.2877726359558888, 3.6289072602398864, 4.206199950403144, 1.8478767445506554, 1.4005840000294698, 2.7643435610122373, 2.260255746568378, 2.349493253959807, 1.292154270266229, 2.8706380949429504, 2.286318256258422, 2.7669434566654116, 2.231581205461338, 4.208344107033454, 1.789205048223616, 3.2378614622582442, 2.356714397109737, 3.3169196999586337], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a5616d90&gt;: [0.825809577961986, 0.8517487747299568, 0.8530699800840803, 0.8205344913952529, 0.8816791998152296, 0.8430880534964709, 0.8393031939426615, 0.8786145516790705, 0.8637312564568208, 0.9146526025917114, 0.8226869864456329, 0.9101093330580857, 0.8802669584890603, 0.899810759930522, 0.8384798676407728, 0.9698380872312293, 0.867029947724181, 0.8591930677450709, 0.9176158151231272, 0.8633993837314099], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fd7a53fa090&gt;: [0.8013935080870905, 0.8356003248179015, 0.8594949074777191, 0.8264024970949583, 0.8954895604613964, 0.8264983527173453, 0.8546491222732131, 0.8620632162427301, 0.8164993173850382, 0.8943565683407572, 0.8280003853175805, 0.9010307438097649, 0.8477783455714307, 0.8572576859252351, 0.8199677425088564, 0.9436551384377027, 0.8602391812964473, 0.8580532199221257, 0.9338507456214542, 0.84602074977914], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a567b410&gt;: [2.5848662641224514, 1.6536202679180994, 1.6004990541947341, 1.4162279321436937, 1.556260701498988, 1.2517712879314555, 1.9146369993130006, 1.1361195681455483, 0.9872472155020233, 5.1916844653945144, 1.0575695007272854, 1.6561512135836984, 3.2854069825200307, 1.4165270091862991, 2.003385991201208, 1.7836795855244294, 1.3332161294359355, 3.6347305092325266, 2.816609062083931, 1.7290588846629014], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55f5b50&gt;: [0.9523414047912101, 0.9597110088072558, 0.9968666031492821, 1.3410895983862154, 2.298507482535234, 1.069281449012228, 1.2508604674657156, 2.8728229515989008, 0.9773366599711919, 2.2775385009261506, 1.1860527205292184, 2.3425015528700266, 1.3675125330359685, 2.201440035654539, 2.19032978136693, 1.217725411823086, 1.1059813501386746, 1.3176603484679843, 1.3570936227590322, 1.0300414274214569], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fd7a55f53d0&gt;: [1.0751386553049695, 1.112066315274249, 1.3559188422895607, 1.3078930073249206, 2.3372816799779503, 0.9744807249516403, 1.3371436404897052, 1.3672306170938855, 2.4611684894765795, 1.4276596782879372, 1.7261025185308123, 1.1047831501931211, 1.5204216540267894, 1.7365264896038322, 1.594625276726357, 1.7115300673273752, 1.2664567414363919, 1.8095336908121362, 2.4185682235628705, 1.3526697430092898], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd796cd8c90&gt;: [0.8351344457251998, 0.8615086053538248, 0.8785883073083322, 0.986209499615214, 1.021984133744527, 0.9205520184601708, 0.886865854079548, 1.0173013962513702, 0.9164868317618675, 1.1110994296062995, 0.9124605049572495, 1.0252608063559865, 0.8844999615471015, 0.9038031215788342, 0.9131763668550934, 1.0273593151226688, 1.0266124699143933, 1.0509141712383183, 1.0264138983957292, 0.8783613081584485], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a56a1950&gt;: [0.947545035633579, 0.9555080888677053, 0.9792016331304672, 1.0439007412824606, 1.0248889133176808, 0.8821338301047318, 0.9608532865592169, 0.9735707532363934, 1.0074624421818459, 1.0476350479643601, 1.0450864638664898, 0.994806891983797, 1.0057603020827646, 0.9396584526263347, 1.0191244988388064, 1.0456683359752783, 1.0539098087434597, 1.0263300707835907, 1.0796254836849781, 1.052126793018059], &lt;method-wrapper \'__str__\' of SVC object at 0x7fd7a56a6190&gt;: [0.8717788263856254, 0.8796127705783189, 0.9215725743921747, 0.9952553377074833, 1.054725919476, 0.9182395147403436, 0.8880198544978372, 1.0660884738746164, 0.9324344859712136, 1.1184781487911724, 0.9414273005417741, 1.058429238752157, 0.9039331851653729, 0.9239760972876739, 0.948515468912744, 1.1366051826462378, 1.0488848287448331, 1.0487096983248425, 1.1294975737796635, 0.9092613191308369], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a53b3050&gt;: [16.52000780334536, 14.517582615061075, 18.021826694558577, 14.016976317990004, 13.516370020918933, 19.023039288700716, 14.517582615061075, 15.51879520920322, 13.516370020918933, 16.52000780334536, 17.020614100416434, 16.019401506274292, 15.018188912132148, 18.522432991629646, 15.518795209203217, 20.52485817991393, 16.52000780334536, 16.019401506274292, 17.020614100416434, 17.020614100416434], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a568b290&gt;: [6.883177377768846, 6.369672285532876, 7.838614459883151, 6.415447797560713, 7.806461576369366, 9.38293711213375, 6.351142030533141, 6.906427050457342, 6.367312576688495, 6.932948474136293, 7.850601212901974, 7.404673638684033, 7.380511923849462, 6.4323421770652205, 7.88275409641576, 8.473275542047283, 7.942152236957652, 6.335159693174709, 6.944211393805962, 7.877122636580926], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fd7a5684550&gt;: [4.542410066371891, 4.046285611046485, 4.025411320999311, 3.6281702660027597, 6.886198601564255, 4.089372018026924, 4.518922817740299, 3.5930907014984785, 4.044837944348179, 4.589238807951901, 4.566161670263385, 6.0525495224673405, 5.525199899571164, 4.570961802692204, 5.465062251883179, 5.568098097754681, 6.0531321684103965, 3.9995486897263977, 4.085031363687356, 4.086682912979525]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86f04ae50&gt;: [0.9296471456736545, 3.2755839396297906, 2.285403039146306, 3.193903321523394, 3.1252636131554143, 3.169919927520543, 2.358429594033986, 2.259017846252404, 2.690426423607163, 2.71677121015267, 4.21312539069929, 1.8569426024107234, 2.749709792992684, 1.3518818070111367, 2.2725355915752905, 1.8722629723970772, 2.750498103184609, 1.8526606390821883, 1.2981052383388803, 2.271105380328932], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff864171650&gt;: [0.8292593208360692, 0.8720065675820574, 0.8431386031026222, 0.8640075411930045, 0.807841615123259, 0.8564028674867811, 1.351673362035366, 0.7831487329852416, 0.8386479317073138, 0.8510765315637783, 0.8965361103638416, 0.8614577745734677, 0.8871062339391858, 0.8604689698983513, 0.8226206038909196, 0.8618757048377585, 0.9050446210765668, 0.8250643886288854, 0.8066306767137665, 0.8272744681211341], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff86f04c110&gt;: [0.8051925960482706, 0.8591977620181789, 0.8414585172175385, 0.8749446567268365, 0.8267237251342769, 0.8449941989748808, 0.9172153369932607, 0.7856490679484761, 0.826346294037664, 0.864794680619914, 0.8788048542833887, 0.8431287440869767, 0.855658219643593, 0.8276169725247706, 0.797033796687518, 0.8629702403385286, 0.8909958617104965, 0.8339186007925439, 0.7967007794323998, 0.8364902108534128], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff864177c90&gt;: [0.7767820903775472, 4.300686838074431, 2.0207147682219224, 1.5944113459212481, 1.0759356136091138, 1.3185398032640891, 2.224981482773766, 1.0940190710027042, 1.5638934632824073, 1.409995343834862, 1.6931829892101609, 1.1731728240167665, 1.4140958381439543, 1.4158761992591087, 1.1968547615653309, 1.0911017661686355, 1.7687451473644522, 1.9648133025864472, 1.1703843047199323, 1.2705774200971864], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86edd5850&gt;: [0.8946497845248328, 1.074497433341399, 0.83297562807642, 1.465452897553748, 0.9265145557094644, 1.0020047421277356, 1.2605155253707876, 0.8881353125540851, 1.1298992607573775, 1.7550421181212568, 1.150166272017814, 1.3555326818033822, 0.9793054523632743, 1.2054787780121692, 1.1718886925184044, 1.3049693680564367, 1.2991066188329887, 0.8414245073920219, 1.0822655125179947, 1.206934744505767], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff86414a990&gt;: [1.3195715484129118, 1.3097819564608393, 1.0990742309179051, 2.983180581207407, 1.1121014475918607, 1.574497495734434, 1.3682897814275694, 2.234828128121864, 2.526917167930214, 2.0782501760697514, 1.8579980620231558, 3.2744609599693124, 1.0486079782081652, 1.5778456167199755, 1.1213951597261635, 1.4260739975878511, 2.8707116945217575, 1.5349132317355698, 1.5239098686760253, 1.586173287947651], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff864157390&gt;: [0.846745697577985, 0.9365098430079123, 0.8127468400439247, 1.058686321163429, 0.8766920160754863, 0.9028681502382009, 1.0240089461515902, 0.780036117183776, 0.8763704503983293, 0.9682330105159463, 0.9828088743531325, 0.9471234859251724, 0.9187510023515743, 0.9389858574784498, 0.9211866469434261, 0.9558905649260149, 0.986841483764418, 0.7752854223920571, 0.8124277204586572, 0.9915180648344053], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86414f810&gt;: [0.9719963887137961, 0.982763412913783, 0.9292081432690931, 1.0490078707657091, 0.9744574219407257, 0.9369524111404659, 1.0259671748590788, 0.8624595691985374, 1.0061256511057874, 0.9870904397153519, 1.0455705392126815, 0.9852390803139142, 0.9743876526390333, 1.07047718439584, 0.9541079070322829, 0.9941646285910011, 1.0314131972281375, 0.9417509805392987, 0.9444278774609942, 1.0677062320623452], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff86414e210&gt;: [0.8624872926631665, 0.9356126511784255, 0.8338820354957703, 1.0320227447852526, 0.8327305987685345, 0.8971713541784685, 1.0215352152931938, 0.7682745080353075, 0.8556335182165802, 0.9688130027023312, 0.9830514352410383, 0.9459486479294854, 0.9207955679663924, 0.9815373606631472, 0.9246866104222211, 0.9284638611814131, 0.9448207439983276, 0.7737230826082588, 0.8647461133121621, 1.0076003233114714], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86ef562d0&gt;: [13.015763723847861, 14.016976317990006, 16.019401506274292, 14.517582615061075, 14.016976317990006, 13.516370020918933, 15.018188912132148, 16.019401506274292, 13.516370020918933, 15.518795209203217, 14.517582615061075, 14.016976317990004, 14.016976317990006, 13.015763723847861, 16.52000780334536, 13.516370020918933, 15.018188912132148, 13.516370020918933, 15.018188912132144, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86efdf990&gt;: [3.9253151073702544, 8.311063457780044, 4.427557279936554, 8.798770959686218, 4.934518870191614, 5.910845916150034, 8.282906158605865, 5.0084516813936295, 4.892738942503383, 9.35242010411519, 7.783935737030022, 5.375003193371644, 5.3628282315558975, 7.35798608451012, 3.9565559487379662, 6.348782321688761, 6.86628299826434, 4.907997446512663, 7.843333877571912, 5.983866685205975], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff86efdd6d0&gt;: [3.5777403772292775, 5.457481194147039, 3.093855924662732, 5.468490864076674, 3.548292272559831, 4.478449369344279, 6.443856500742844, 4.536778606537055, 2.573930498299657, 5.562482311716788, 5.941128070770487, 4.514819739343827, 3.9963576534760006, 4.025238785999331, 2.1080743695298483, 4.012685060834393, 5.048410247334703, 3.939821152981489, 4.509280099768914, 3.5748136962387824]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f041487f710&gt;: [3.710670276784618, 1.279656625246626, 2.2525939740921803, 2.349160682790747, 1.758296778024964, 1.2787141626740894, 2.701851990311612, 1.271723220411021, 1.769815656257101, 1.7360515318428098, 1.7494554331767485, 2.2564757144428413, 1.3048805304311477, 1.762520977509888, 3.2811567084535933, 0.8361218891219521, 1.7315508413341618, 1.8539456587457168, 1.2275217179013358, 1.3044184414761995], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0414879d90&gt;: [0.8928641070513107, 0.8480386255948656, 0.8188350070582779, 0.8850164658568429, 0.782087996210172, 0.8001768747132784, 0.8535715753290543, 0.7552674283451182, 0.8053737362712317, 0.7819613906872876, 0.7993271057492495, 0.8310071093583367, 0.8101971149856069, 1.2544085404516299, 0.8862826116839158, 0.7951819275480436, 0.8474788677630676, 0.8311367305316101, 0.7851506132537117, 0.8039552890402156], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0405ae7f10&gt;: [0.9022770373275394, 0.776122652063406, 0.8242983692932587, 0.8783305915320884, 0.7548535842771334, 0.762325198992701, 0.8317234765234836, 0.787727410991896, 0.792967380466929, 0.7798101774422945, 0.7953376481018725, 0.810263744732281, 0.8075270736861953, 0.7706226076667763, 0.8571090501228004, 0.7763804838201245, 0.8158218083784955, 0.8089505806402602, 0.7709847414498687, 0.7714131116488705], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0414894d90&gt;: [4.790464721377591, 2.1543975934244854, 1.4844027921409726, 1.9565721809963488, 5.085072029732825, 1.4182176847489067, 0.9760568471418412, 4.138562962111132, 3.7256353761937913, 1.2320189022075412, 1.0112601322415335, 2.2724661813064193, 4.945373273242598, 0.7492644104389119, 1.6507755227346763, 0.9924222173636836, 2.8785829539525616, 1.409882309298914, 1.4585352590061669, 6.356219548475995], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0414887990&gt;: [2.2772184659189163, 0.7254193359226733, 2.8381990444507754, 1.7814734250532414, 1.1851392377013932, 1.8946552985772327, 0.9787797433473341, 1.0816584753578493, 0.8554843872732053, 0.914894682318551, 0.8772646536198868, 1.0443157722707082, 0.9056415916643314, 0.7488494934884119, 1.3595667229626294, 0.6884199686287269, 1.0430833053603445, 0.9498021274966663, 1.9160375095575166, 0.8874467615268158], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f04148c2410&gt;: [2.136999699893998, 0.7899755037194843, 3.2027623979162296, 1.4105556054514454, 1.9262269535918846, 0.6808310701630548, 1.0033274142296669, 0.9663199079467909, 1.6416770104663931, 1.2416238344808859, 0.8281211708506802, 0.9770643435338998, 2.2937710973997203, 0.8380258630882889, 2.6495198930554027, 0.9087943150504757, 1.1036913976758262, 0.8670599406829134, 1.3833419379370622, 1.0695713417376096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04148c2250&gt;: [0.9743169141009312, 0.7212903336652503, 0.8860672814194667, 1.0592553795033748, 0.8270139169394091, 0.774325247642333, 0.8363619403923024, 0.9002659542274041, 0.772406016748644, 0.7881470135193804, 0.8223505684179271, 0.8834780613909179, 0.8673614462277364, 0.804624296931673, 0.8745523847952291, 0.818107054067621, 0.8634936693276004, 0.7903943849823786, 0.8024422877882996, 0.8295707776024911], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04148c1c50&gt;: [1.065059454815505, 0.8928350342092948, 0.9748650143683305, 1.0836348917835572, 0.9560207627911674, 0.9245120220635727, 0.9806079235791962, 0.9816626603034019, 0.9401622123852125, 0.9993532428130791, 0.9796528884247068, 0.9576988095267276, 0.976056922616288, 0.9760093569960091, 1.0192782289501316, 0.9506493644875174, 0.9887641484300088, 1.003649967691067, 0.9384463536160776, 0.982144784923144], &lt;method-wrapper \'__str__\' of SVC object at 0x7f04148c2f10&gt;: [1.0068886656154366, 0.7441295435123152, 0.8998805863393868, 1.074350110635871, 0.7757289926633537, 0.7731436268523526, 0.8932301908251221, 0.8540003899482328, 0.7174008226968563, 0.772874561173209, 0.810047163051818, 0.929377895804629, 0.7998627206944827, 0.8459887188990982, 0.9318234012468685, 0.7878266081207858, 0.9059890144722537, 0.8976595454683438, 0.8509396372537034, 0.8549087303233748], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04148b12d0&gt;: [16.52000780334536, 13.01576372384786, 16.52000780334536, 15.018188912132148, 11.013338535563573, 13.015763723847861, 15.018188912132148, 15.51879520920322, 14.016976317990004, 14.016976317990006, 13.015763723847861, 13.516370020918933, 15.518795209203217, 13.015763723847861, 14.016976317990004, 10.01212594142143, 17.020614100416434, 11.513944832634646, 14.016976317990006, 16.52000780334536], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04148c18d0&gt;: [7.816812453892961, 3.936578027039926, 7.840974168727531, 9.27776345956402, 5.305789799858388, 6.876822084584857, 5.827286060773575, 7.342003747151687, 5.874697448296639, 6.402549002395814, 4.8983704023382195, 7.8048257008741375, 6.407456628881498, 5.8505357334620705, 7.333100536326397, 5.390985530730075, 6.913694385787404, 5.823290476433966, 7.765405482030287, 5.954261719333491], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f04148eda50&gt;: [5.492415002968147, 2.5916137520964337, 4.518750282740319, 5.974069828576543, 3.9317649433591573, 2.5885302099029, 3.5173001126550805, 3.1325366363604865, 2.51926744924347, 5.50937442341577, 4.967555170802584, 5.424351227544062, 3.0845582766913067, 3.534194492159587, 5.455699562968637, 1.1403054643967592, 4.567123079555635, 5.428929457826728, 5.4109011340299915, 2.6317578042894354]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2dbac290&gt;: [1.3435885855460523, 2.2442545604469633, 1.3710772043489914, 1.362476046309569, 2.324493861787137, 1.7345362133356899, 2.6962205304767757, 1.2535842275913796, 1.382968962141852, 2.200909584038361, 1.7643383488028763, 2.29081894676707, 2.2839396986510585, 1.8135120525977462, 1.8777738752438056, 1.245078064777921, 2.3859769038479586, 2.197018882889919, 3.755608111474356, 3.1969894745826255], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd2d8c2a10&gt;: [0.8352141717714462, 0.788633483127932, 0.9136216080240421, 0.8463948500039051, 0.8396051393060605, 0.8670712103387531, 0.844894090174539, 0.8117828684148154, 0.808455695989969, 0.8147422386268406, 0.8155620225233824, 0.8453318823520164, 0.9325056992338057, 0.8401322361496982, 0.8592048768444984, 0.8136736881105754, 0.9250593253661616, 0.8307421806668063, 0.9093725645031374, 0.7969241960077523], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdd1a144d50&gt;: [0.837777949941547, 0.797844768991122, 0.8398823137403529, 0.8389136602737572, 0.8156411674481059, 0.8621456963694121, 0.8139098694313511, 0.8417688803915474, 0.8186475776862902, 0.8154799994897053, 0.833764129556227, 0.8098508058228875, 0.9365896431745784, 0.8131108789133031, 0.8684141665097728, 0.8412502927768948, 0.9065824167721784, 0.8284556913026956, 0.8902651479399091, 0.7857667519507502], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd1a144dd0&gt;: [3.563587402860059, 3.1037049494002527, 4.154451111234915, 2.6647842448724077, 3.2351785352373192, 1.1684664110215492, 2.790320188054378, 5.849476211072613, 2.207971524822606, 2.702949482279421, 1.51754831224752, 3.530725651995911, 1.4423184995698375, 1.8427375143737459, 4.120545940367783, 1.3733850575196127, 2.3005135072723597, 1.4684185012195405, 1.5745159816804628, 2.572122236504315], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2db83190&gt;: [0.9634785708689044, 1.0557893210356022, 0.8703979333398225, 1.0671897929837988, 1.027269033639198, 1.1720735409107381, 1.6912463649526097, 1.0570759763097384, 0.7977754992042945, 1.0846312028934235, 2.796741283462553, 0.9488576507471035, 1.713126085685816, 1.0719711968715488, 3.5289799790899785, 1.2082598184076734, 3.1450608150536934, 0.8021797160654986, 1.246373808852096, 1.1561500070836144], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdd2dbc1990&gt;: [3.658456876935623, 0.9379159202085757, 3.8337185223467785, 1.0813049930349972, 1.4325302154153141, 3.468652573817179, 2.5861880149706735, 4.034624743576703, 2.296862517723704, 3.200613187775571, 1.45441704618438, 1.2598568131261745, 1.64102787822565, 1.0042447768010667, 1.4939347666982643, 2.4996350679269104, 1.568116618530849, 2.7989677213489004, 1.722205387371533, 1.007555046059085], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd2dbac410&gt;: [0.975852069104445, 0.7662304405257956, 0.751479864969181, 0.8859105470979851, 0.8499019593539399, 0.9200985145549878, 0.8329679594233887, 0.9098442577068566, 0.7617228392061427, 0.8494397988917842, 0.8422933766441789, 0.7883418683530015, 1.04195287031448, 0.8368424102847245, 0.8573473074696544, 0.8167271142251509, 0.9394752129844279, 0.7365680315772657, 0.9466708011092003, 0.8777284630511928], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1eb2e8d0&gt;: [1.0886112042050655, 0.9112727412932082, 0.9860602519688287, 0.9077863968710207, 0.9550714061603262, 0.919071057543887, 0.9609301853694832, 0.957720048083019, 0.9560303408281317, 1.0203367766588143, 0.9452055849527731, 0.9348115148801033, 1.1095696699234305, 0.9747234950428426, 1.051495698073114, 0.9697039130502062, 1.0166128144542022, 0.9611856905091819, 1.0723902077113285, 0.9254878797676793], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdd1eb2e010&gt;: [0.9467639567156552, 0.7614278381229526, 0.7666718050205427, 0.8831112847382169, 0.8147703868070059, 0.9073336880654277, 0.8863324343659622, 0.8335011409134325, 0.762822424996328, 0.8976510566008312, 0.8418223860740359, 0.7707321785384104, 1.0553806557970646, 0.8342254157206285, 0.8703470061820135, 0.8745910809264692, 0.9845104386298082, 0.7932614353367325, 0.9225967009504958, 0.8739338097533182], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1a144e90&gt;: [10.512732238492504, 11.013338535563575, 9.010913347279288, 13.015763723847861, 10.512732238492504, 13.516370020918933, 11.513944832634646, 11.013338535563575, 11.513944832634646, 13.015763723847861, 11.513944832634646, 12.515157426776788, 13.015763723847861, 14.016976317990006, 13.015763723847861, 14.016976317990002, 12.515157426776788, 14.517582615061075, 11.513944832634646, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1eb2eb50&gt;: [5.851447775608144, 5.80875580577384, 5.290531295849108, 3.4744799066666294, 3.4270685191435635, 4.407391149441591, 4.8476872638246995, 5.358108813867137, 2.916835177898049, 4.445175492790214, 5.393345239574456, 3.902789268030912, 5.343574143207009, 6.399465460202281, 6.343874695203078, 5.922108835819706, 8.284542034101094, 4.961764127219717, 5.349205603041845, 5.290531295849108], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdd1eb2f490&gt;: [5.011036014929157, 3.4827875202969136, 2.990344926905038, 2.6696990088410955, 2.5556534930399604, 3.5226021762868975, 4.013910825386544, 1.587712052906891, 1.5836357538272254, 3.0629444794980394, 3.536872491687122, 3.0467245661965108, 3.0683383633897785, 2.138418842548427, 4.042635096706836, 2.5907173837473, 5.942181300322659, 3.578004732489179, 4.055598932814851, 2.5388509337953757]}'}</t>
-  </si>
-  <si>
     <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
     <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
   </si>
 </sst>
 </file>
@@ -699,40 +675,40 @@
         <v>48</v>
       </c>
       <c r="F2">
-        <v>0.8837134395424837</v>
+        <v>0.9015277777777777</v>
       </c>
       <c r="G2">
-        <v>0.03606643693547368</v>
+        <v>0.02944853876145952</v>
       </c>
       <c r="H2">
-        <v>0.7444444444444445</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I2">
-        <v>0.04779069592801461</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="J2">
-        <v>0.6843504901960784</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="K2">
-        <v>0.05410891862244693</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="L2">
-        <v>0.6866173482949799</v>
+        <v>0.7545833333333334</v>
       </c>
       <c r="M2">
-        <v>0.1120180830599318</v>
+        <v>0.09180292902613608</v>
       </c>
       <c r="N2">
-        <v>0.6843504901960784</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="O2">
-        <v>0.05410891862244693</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="P2">
-        <v>0.6658281664807557</v>
+        <v>0.6854599567099566</v>
       </c>
       <c r="Q2">
-        <v>0.07443724014439218</v>
+        <v>0.07050057928488081</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -740,7 +716,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
@@ -749,40 +725,40 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>0.8829669117647058</v>
+        <v>0.9015277777777777</v>
       </c>
       <c r="G3">
-        <v>0.03623239709852213</v>
+        <v>0.0292307497063463</v>
       </c>
       <c r="H3">
-        <v>0.7444444444444445</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I3">
-        <v>0.04779069592801461</v>
+        <v>0.04969039949999535</v>
       </c>
       <c r="J3">
-        <v>0.6843504901960784</v>
+        <v>0.6945833333333333</v>
       </c>
       <c r="K3">
-        <v>0.05410891862244693</v>
+        <v>0.07061977610965486</v>
       </c>
       <c r="L3">
-        <v>0.6866173482949799</v>
+        <v>0.7470238095238095</v>
       </c>
       <c r="M3">
-        <v>0.1120180830599318</v>
+        <v>0.1298110435574665</v>
       </c>
       <c r="N3">
-        <v>0.6843504901960784</v>
+        <v>0.6945833333333333</v>
       </c>
       <c r="O3">
-        <v>0.05410891862244693</v>
+        <v>0.07061977610965486</v>
       </c>
       <c r="P3">
-        <v>0.6658281664807557</v>
+        <v>0.692465834818776</v>
       </c>
       <c r="Q3">
-        <v>0.07443724014439218</v>
+        <v>0.08539015914303033</v>
       </c>
       <c r="R3" t="s">
         <v>50</v>
@@ -799,92 +775,98 @@
         <v>48</v>
       </c>
       <c r="F4">
-        <v>0.8818176062091503</v>
+        <v>0.9002777777777778</v>
       </c>
       <c r="G4">
-        <v>0.03614440159514244</v>
+        <v>0.02291182608810039</v>
       </c>
       <c r="H4">
-        <v>0.7444444444444445</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I4">
-        <v>0.04779069592801461</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J4">
-        <v>0.6843504901960784</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K4">
-        <v>0.05410891862244693</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L4">
-        <v>0.6866173482949799</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M4">
-        <v>0.1120180830599318</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N4">
-        <v>0.6843504901960784</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O4">
-        <v>0.05410891862244693</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P4">
-        <v>0.6658281664807557</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q4">
-        <v>0.07443724014439218</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
       </c>
       <c r="F5">
-        <v>0.8787336601307191</v>
+        <v>0.8999305555555557</v>
       </c>
       <c r="G5">
-        <v>0.04023793691297004</v>
+        <v>0.02721690707748033</v>
       </c>
       <c r="H5">
-        <v>0.7222222222222221</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I5">
-        <v>0.06334307917217435</v>
+        <v>0.06478835438717004</v>
       </c>
       <c r="J5">
-        <v>0.6460171568627452</v>
+        <v>0.7129166666666665</v>
       </c>
       <c r="K5">
-        <v>0.07077046195465235</v>
+        <v>0.07470311610338323</v>
       </c>
       <c r="L5">
-        <v>0.6885650288823664</v>
+        <v>0.71375</v>
       </c>
       <c r="M5">
-        <v>0.1483157972434721</v>
+        <v>0.1548049848465266</v>
       </c>
       <c r="N5">
-        <v>0.6460171568627452</v>
+        <v>0.7129166666666665</v>
       </c>
       <c r="O5">
-        <v>0.07077046195465235</v>
+        <v>0.07470311610338323</v>
       </c>
       <c r="P5">
-        <v>0.6178274856216033</v>
+        <v>0.68379329004329</v>
       </c>
       <c r="Q5">
-        <v>0.0805922777848706</v>
+        <v>0.1104203609590559</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -893,243 +875,243 @@
         <v>48</v>
       </c>
       <c r="F6">
-        <v>0.8784503676470589</v>
+        <v>0.8995833333333334</v>
       </c>
       <c r="G6">
-        <v>0.03574709646342157</v>
+        <v>0.02104911401026857</v>
       </c>
       <c r="H6">
-        <v>0.7444444444444445</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I6">
-        <v>0.04444444444444447</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J6">
-        <v>0.6945588235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K6">
-        <v>0.05191283222531768</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L6">
-        <v>0.7328402920179237</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M6">
-        <v>0.08550665324731434</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N6">
-        <v>0.6945588235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O6">
-        <v>0.05191283222531768</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P6">
-        <v>0.6813852553964783</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q6">
-        <v>0.0647637516054075</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>0.8784503676470589</v>
+        <v>0.8993055555555556</v>
       </c>
       <c r="G7">
-        <v>0.03574709646342157</v>
+        <v>0.02705037167997307</v>
       </c>
       <c r="H7">
-        <v>0.7444444444444445</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I7">
-        <v>0.04444444444444447</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="J7">
-        <v>0.6945588235294118</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="K7">
-        <v>0.05191283222531768</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="L7">
-        <v>0.7328402920179237</v>
+        <v>0.7545833333333334</v>
       </c>
       <c r="M7">
-        <v>0.08550665324731434</v>
+        <v>0.09180292902613608</v>
       </c>
       <c r="N7">
-        <v>0.6945588235294118</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="O7">
-        <v>0.05191283222531768</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="P7">
-        <v>0.6813852553964783</v>
+        <v>0.6854599567099566</v>
       </c>
       <c r="Q7">
-        <v>0.0647637516054075</v>
+        <v>0.07050057928488081</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.8784503676470589</v>
+        <v>0.8993055555555556</v>
       </c>
       <c r="G8">
-        <v>0.03574709646342157</v>
+        <v>0.02705037167997307</v>
       </c>
       <c r="H8">
-        <v>0.7444444444444445</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I8">
-        <v>0.04444444444444447</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="J8">
-        <v>0.6945588235294118</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="K8">
-        <v>0.05191283222531768</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="L8">
-        <v>0.7328402920179237</v>
+        <v>0.7545833333333334</v>
       </c>
       <c r="M8">
-        <v>0.08550665324731434</v>
+        <v>0.09180292902613608</v>
       </c>
       <c r="N8">
-        <v>0.6945588235294118</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="O8">
-        <v>0.05191283222531768</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="P8">
-        <v>0.6813852553964783</v>
+        <v>0.6854599567099566</v>
       </c>
       <c r="Q8">
-        <v>0.0647637516054075</v>
+        <v>0.07050057928488081</v>
       </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
       </c>
       <c r="F9">
-        <v>0.8776629901960785</v>
+        <v>0.8990972222222222</v>
       </c>
       <c r="G9">
-        <v>0.03723994527715474</v>
+        <v>0.02777569436631357</v>
       </c>
       <c r="H9">
-        <v>0.7388888888888888</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I9">
-        <v>0.05443310539518176</v>
+        <v>0.06478835438717004</v>
       </c>
       <c r="J9">
-        <v>0.6793504901960784</v>
+        <v>0.7129166666666665</v>
       </c>
       <c r="K9">
-        <v>0.05991685886669434</v>
+        <v>0.07470311610338323</v>
       </c>
       <c r="L9">
-        <v>0.6847234089010404</v>
+        <v>0.71375</v>
       </c>
       <c r="M9">
-        <v>0.1151067083963253</v>
+        <v>0.1548049848465266</v>
       </c>
       <c r="N9">
-        <v>0.6793504901960784</v>
+        <v>0.7129166666666665</v>
       </c>
       <c r="O9">
-        <v>0.05991685886669434</v>
+        <v>0.07470311610338323</v>
       </c>
       <c r="P9">
-        <v>0.6625814132340023</v>
+        <v>0.68379329004329</v>
       </c>
       <c r="Q9">
-        <v>0.07940922656097976</v>
+        <v>0.1104203609590559</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
       </c>
       <c r="F10">
-        <v>0.8772551062091504</v>
+        <v>0.8988194444444444</v>
       </c>
       <c r="G10">
-        <v>0.03625120531001089</v>
+        <v>0.03664772237882667</v>
       </c>
       <c r="H10">
-        <v>0.7388888888888888</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I10">
-        <v>0.05443310539518176</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J10">
-        <v>0.6793504901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="K10">
-        <v>0.05991685886669434</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="L10">
-        <v>0.6847234089010404</v>
+        <v>0.8179166666666667</v>
       </c>
       <c r="M10">
-        <v>0.1151067083963253</v>
+        <v>0.05823801736552051</v>
       </c>
       <c r="N10">
-        <v>0.6793504901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="O10">
-        <v>0.05991685886669434</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="P10">
-        <v>0.6625814132340023</v>
+        <v>0.7343993506493506</v>
       </c>
       <c r="Q10">
-        <v>0.07940922656097976</v>
+        <v>0.06807565975752332</v>
       </c>
       <c r="R10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1137,49 +1119,49 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="F11">
-        <v>0.87571977124183</v>
+        <v>0.89875</v>
       </c>
       <c r="G11">
-        <v>0.0366258187839973</v>
+        <v>0.02415089683430476</v>
       </c>
       <c r="H11">
-        <v>0.7444444444444445</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I11">
-        <v>0.04779069592801461</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="J11">
-        <v>0.6843504901960784</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="K11">
-        <v>0.05410891862244693</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="L11">
-        <v>0.6866173482949799</v>
+        <v>0.7545833333333334</v>
       </c>
       <c r="M11">
-        <v>0.1120180830599318</v>
+        <v>0.09180292902613608</v>
       </c>
       <c r="N11">
-        <v>0.6843504901960784</v>
+        <v>0.7045833333333333</v>
       </c>
       <c r="O11">
-        <v>0.05410891862244693</v>
+        <v>0.07019813229550897</v>
       </c>
       <c r="P11">
-        <v>0.6658281664807557</v>
+        <v>0.6854599567099566</v>
       </c>
       <c r="Q11">
-        <v>0.07443724014439218</v>
+        <v>0.07050057928488081</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1187,296 +1169,296 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
-        <v>0.875501838235294</v>
+        <v>0.8984722222222222</v>
       </c>
       <c r="G12">
-        <v>0.03591725649274708</v>
+        <v>0.02356674753771027</v>
       </c>
       <c r="H12">
-        <v>0.7388888888888888</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I12">
-        <v>0.05443310539518176</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J12">
-        <v>0.6793504901960784</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K12">
-        <v>0.05991685886669434</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L12">
-        <v>0.6847234089010404</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M12">
-        <v>0.1151067083963253</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N12">
-        <v>0.6793504901960784</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O12">
-        <v>0.05991685886669434</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P12">
-        <v>0.6625814132340023</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q12">
-        <v>0.07940922656097976</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>0.8749703839869282</v>
+        <v>0.8984722222222222</v>
       </c>
       <c r="G13">
-        <v>0.0364694698508191</v>
+        <v>0.0197087688856421</v>
       </c>
       <c r="H13">
-        <v>0.7500000000000001</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I13">
-        <v>0.04303314829119354</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J13">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K13">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L13">
-        <v>0.7355142846919163</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M13">
-        <v>0.08565196334787481</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N13">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O13">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P13">
-        <v>0.6847700146297648</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q13">
-        <v>0.06629018846378651</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>0.8743582516339871</v>
+        <v>0.8984027777777778</v>
       </c>
       <c r="G14">
-        <v>0.03459899561709684</v>
+        <v>0.03081612382591816</v>
       </c>
       <c r="H14">
-        <v>0.7277777777777777</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I14">
-        <v>0.05931710140017398</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J14">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K14">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L14">
-        <v>0.7139793612819929</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M14">
-        <v>0.07889670942217106</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N14">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O14">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P14">
-        <v>0.6576014581532409</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q14">
-        <v>0.06508569914246916</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>0.8739554738562092</v>
+        <v>0.8983333333333334</v>
       </c>
       <c r="G15">
-        <v>0.03267546715855747</v>
+        <v>0.03105525740266341</v>
       </c>
       <c r="H15">
-        <v>0.7277777777777777</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I15">
-        <v>0.05931710140017398</v>
+        <v>0.0816496580927726</v>
       </c>
       <c r="J15">
-        <v>0.6731004901960784</v>
+        <v>0.7195833333333332</v>
       </c>
       <c r="K15">
-        <v>0.05675591617240459</v>
+        <v>0.08115485882626569</v>
       </c>
       <c r="L15">
-        <v>0.7139793612819929</v>
+        <v>0.7786309523809523</v>
       </c>
       <c r="M15">
-        <v>0.07889670942217106</v>
+        <v>0.1686861494219449</v>
       </c>
       <c r="N15">
-        <v>0.6731004901960784</v>
+        <v>0.7195833333333332</v>
       </c>
       <c r="O15">
-        <v>0.05675591617240459</v>
+        <v>0.08115485882626569</v>
       </c>
       <c r="P15">
-        <v>0.6576014581532409</v>
+        <v>0.7111598124098124</v>
       </c>
       <c r="Q15">
-        <v>0.06508569914246916</v>
+        <v>0.123171666073365</v>
       </c>
       <c r="R15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
       </c>
       <c r="F16">
-        <v>0.8738662173202615</v>
+        <v>0.8983333333333334</v>
       </c>
       <c r="G16">
-        <v>0.03600868414803432</v>
+        <v>0.02134713637660754</v>
       </c>
       <c r="H16">
-        <v>0.7500000000000001</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I16">
-        <v>0.04303314829119354</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J16">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K16">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L16">
-        <v>0.7355142846919163</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M16">
-        <v>0.08565196334787481</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N16">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O16">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P16">
-        <v>0.6847700146297648</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q16">
-        <v>0.06629018846378651</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="F17">
-        <v>0.8735433006535948</v>
+        <v>0.8977083333333333</v>
       </c>
       <c r="G17">
-        <v>0.03119821025166863</v>
+        <v>0.03591399190865326</v>
       </c>
       <c r="H17">
-        <v>0.7277777777777777</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I17">
-        <v>0.05931710140017398</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J17">
-        <v>0.6731004901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="K17">
-        <v>0.05675591617240459</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="L17">
-        <v>0.7139793612819929</v>
+        <v>0.8179166666666667</v>
       </c>
       <c r="M17">
-        <v>0.07889670942217106</v>
+        <v>0.05823801736552051</v>
       </c>
       <c r="N17">
-        <v>0.6731004901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="O17">
-        <v>0.05675591617240459</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="P17">
-        <v>0.6576014581532409</v>
+        <v>0.7343993506493506</v>
       </c>
       <c r="Q17">
-        <v>0.06508569914246916</v>
+        <v>0.06807565975752332</v>
       </c>
       <c r="R17" t="s">
         <v>51</v>
@@ -1484,152 +1466,152 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="F18">
-        <v>0.8729334150326796</v>
+        <v>0.8977083333333333</v>
       </c>
       <c r="G18">
-        <v>0.03552864265006633</v>
+        <v>0.03591399190865326</v>
       </c>
       <c r="H18">
-        <v>0.7444444444444445</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I18">
-        <v>0.04779069592801461</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J18">
-        <v>0.6843504901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="K18">
-        <v>0.05410891862244693</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="L18">
-        <v>0.6866173482949799</v>
+        <v>0.8179166666666667</v>
       </c>
       <c r="M18">
-        <v>0.1120180830599318</v>
+        <v>0.05823801736552051</v>
       </c>
       <c r="N18">
-        <v>0.6843504901960784</v>
+        <v>0.74625</v>
       </c>
       <c r="O18">
-        <v>0.05410891862244693</v>
+        <v>0.05134307266916455</v>
       </c>
       <c r="P18">
-        <v>0.6658281664807557</v>
+        <v>0.7343993506493506</v>
       </c>
       <c r="Q18">
-        <v>0.07443724014439218</v>
+        <v>0.06807565975752332</v>
       </c>
       <c r="R18" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="F19">
-        <v>0.8718758169934639</v>
+        <v>0.897638888888889</v>
       </c>
       <c r="G19">
-        <v>0.0349336719680922</v>
+        <v>0.02389070568026888</v>
       </c>
       <c r="H19">
-        <v>0.7500000000000001</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I19">
-        <v>0.04303314829119354</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J19">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K19">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L19">
-        <v>0.7355142846919163</v>
+        <v>0.6970833333333334</v>
       </c>
       <c r="M19">
-        <v>0.08565196334787481</v>
+        <v>0.1372067580130237</v>
       </c>
       <c r="N19">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O19">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P19">
-        <v>0.6847700146297648</v>
+        <v>0.6571266233766233</v>
       </c>
       <c r="Q19">
-        <v>0.06629018846378651</v>
+        <v>0.09024712760645696</v>
       </c>
       <c r="R19" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="F20">
-        <v>0.8716235702614379</v>
+        <v>0.8971527777777778</v>
       </c>
       <c r="G20">
-        <v>0.03529311252748318</v>
+        <v>0.03156966136211342</v>
       </c>
       <c r="H20">
-        <v>0.75</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I20">
-        <v>0.04648111258522644</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J20">
-        <v>0.6926838235294117</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K20">
-        <v>0.05506677980315605</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="L20">
-        <v>0.6929818171594487</v>
+        <v>0.77125</v>
       </c>
       <c r="M20">
-        <v>0.1142571177093064</v>
+        <v>0.1079351657246145</v>
       </c>
       <c r="N20">
-        <v>0.6926838235294117</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O20">
-        <v>0.05506677980315605</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="P20">
-        <v>0.6750552196208522</v>
+        <v>0.7121266233766234</v>
       </c>
       <c r="Q20">
-        <v>0.07778102565913232</v>
+        <v>0.08664486506137982</v>
       </c>
       <c r="R20" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1637,54 +1619,54 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="F21">
-        <v>0.870515727124183</v>
+        <v>0.8971527777777778</v>
       </c>
       <c r="G21">
-        <v>0.03510483058938768</v>
+        <v>0.03365040173663666</v>
       </c>
       <c r="H21">
-        <v>0.7500000000000001</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I21">
-        <v>0.04303314829119354</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J21">
-        <v>0.6976838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K21">
-        <v>0.05261189981929144</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="L21">
-        <v>0.7355142846919163</v>
+        <v>0.77125</v>
       </c>
       <c r="M21">
-        <v>0.08565196334787481</v>
+        <v>0.1079351657246145</v>
       </c>
       <c r="N21">
-        <v>0.6976838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O21">
-        <v>0.05261189981929144</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="P21">
-        <v>0.6847700146297648</v>
+        <v>0.7121266233766234</v>
       </c>
       <c r="Q21">
-        <v>0.06629018846378651</v>
+        <v>0.08664486506137982</v>
       </c>
       <c r="R21" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>47</v>
@@ -1693,93 +1675,93 @@
         <v>48</v>
       </c>
       <c r="F22">
-        <v>0.8687387663398694</v>
+        <v>0.8967361111111112</v>
       </c>
       <c r="G22">
-        <v>0.03795499989328438</v>
+        <v>0.03314006470858032</v>
       </c>
       <c r="H22">
-        <v>0.7555555555555556</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I22">
-        <v>0.04082482904638632</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J22">
-        <v>0.7026838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K22">
-        <v>0.04627281888215845</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="L22">
-        <v>0.7305900422676739</v>
+        <v>0.77125</v>
       </c>
       <c r="M22">
-        <v>0.06145366272927493</v>
+        <v>0.1079351657246145</v>
       </c>
       <c r="N22">
-        <v>0.7026838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O22">
-        <v>0.04627281888215845</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="P22">
-        <v>0.6907324655612561</v>
+        <v>0.7121266233766234</v>
       </c>
       <c r="Q22">
-        <v>0.05493656417929033</v>
+        <v>0.08664486506137982</v>
       </c>
       <c r="R22" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="F23">
-        <v>0.8686076388888889</v>
+        <v>0.8955555555555555</v>
       </c>
       <c r="G23">
-        <v>0.03225090467914752</v>
+        <v>0.02151814300526559</v>
       </c>
       <c r="H23">
-        <v>0.7277777777777777</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I23">
-        <v>0.05931710140017398</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J23">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K23">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L23">
-        <v>0.7139793612819929</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M23">
-        <v>0.07889670942217106</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N23">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O23">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P23">
-        <v>0.6576014581532409</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q23">
-        <v>0.06508569914246916</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1787,49 +1769,49 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="F24">
-        <v>0.8680341094771242</v>
+        <v>0.8947916666666668</v>
       </c>
       <c r="G24">
-        <v>0.03455963090459725</v>
+        <v>0.03160294514717429</v>
       </c>
       <c r="H24">
-        <v>0.7500000000000001</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="I24">
-        <v>0.04303314829119354</v>
+        <v>0.06085806194501849</v>
       </c>
       <c r="J24">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="K24">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="L24">
-        <v>0.7355142846919163</v>
+        <v>0.7105681818181818</v>
       </c>
       <c r="M24">
-        <v>0.08565196334787481</v>
+        <v>0.1515880695749687</v>
       </c>
       <c r="N24">
-        <v>0.6976838235294118</v>
+        <v>0.6879166666666666</v>
       </c>
       <c r="O24">
-        <v>0.05261189981929144</v>
+        <v>0.07824463062870336</v>
       </c>
       <c r="P24">
-        <v>0.6847700146297648</v>
+        <v>0.6650798397508924</v>
       </c>
       <c r="Q24">
-        <v>0.06629018846378651</v>
+        <v>0.1019204187636971</v>
       </c>
       <c r="R24" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1837,54 +1819,54 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="F25">
-        <v>0.8672303921568627</v>
+        <v>0.8942361111111111</v>
       </c>
       <c r="G25">
-        <v>0.03342343759153761</v>
+        <v>0.03153542491693045</v>
       </c>
       <c r="H25">
-        <v>0.7500000000000001</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I25">
-        <v>0.04303314829119354</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="J25">
-        <v>0.6976838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K25">
-        <v>0.05261189981929144</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="L25">
-        <v>0.7355142846919163</v>
+        <v>0.77125</v>
       </c>
       <c r="M25">
-        <v>0.08565196334787481</v>
+        <v>0.1079351657246145</v>
       </c>
       <c r="N25">
-        <v>0.6976838235294118</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O25">
-        <v>0.05261189981929144</v>
+        <v>0.05960518247415891</v>
       </c>
       <c r="P25">
-        <v>0.6847700146297648</v>
+        <v>0.7121266233766234</v>
       </c>
       <c r="Q25">
-        <v>0.06629018846378651</v>
+        <v>0.08664486506137982</v>
       </c>
       <c r="R25" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
@@ -1893,190 +1875,190 @@
         <v>48</v>
       </c>
       <c r="F26">
-        <v>0.8641903594771241</v>
+        <v>0.8939583333333333</v>
       </c>
       <c r="G26">
-        <v>0.03526942478086516</v>
+        <v>0.02495134153596643</v>
       </c>
       <c r="H26">
         <v>0.7444444444444445</v>
       </c>
       <c r="I26">
-        <v>0.03239417719358502</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J26">
-        <v>0.6947426470588235</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K26">
-        <v>0.04038575748255124</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L26">
-        <v>0.7143253968253969</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M26">
-        <v>0.05415256753231699</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N26">
-        <v>0.6947426470588235</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O26">
-        <v>0.04038575748255124</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P26">
-        <v>0.6792136875689507</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q26">
-        <v>0.0425219375723415</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R26" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="F27">
-        <v>0.8626521650326797</v>
+        <v>0.8936111111111111</v>
       </c>
       <c r="G27">
-        <v>0.03315628697299386</v>
+        <v>0.02596293654566204</v>
       </c>
       <c r="H27">
-        <v>0.7277777777777777</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I27">
-        <v>0.05931710140017398</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J27">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K27">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L27">
-        <v>0.7139793612819929</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M27">
-        <v>0.07889670942217106</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N27">
-        <v>0.6731004901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O27">
-        <v>0.05675591617240459</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P27">
-        <v>0.6576014581532409</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q27">
-        <v>0.06508569914246916</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="F28">
-        <v>0.8623084150326796</v>
+        <v>0.8925694444444444</v>
       </c>
       <c r="G28">
-        <v>0.03316442753673486</v>
+        <v>0.02324014127897391</v>
       </c>
       <c r="H28">
-        <v>0.7222222222222222</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I28">
-        <v>0.06573421981221798</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J28">
-        <v>0.6699754901960785</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K28">
-        <v>0.05901524874381626</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L28">
-        <v>0.7049317422343737</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M28">
-        <v>0.09108177169987271</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N28">
-        <v>0.6699754901960785</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O28">
-        <v>0.05901524874381626</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P28">
-        <v>0.6537727331148384</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q28">
-        <v>0.06880973249910666</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="F29">
-        <v>0.8615559640522875</v>
+        <v>0.8922916666666666</v>
       </c>
       <c r="G29">
-        <v>0.03506618805803233</v>
+        <v>0.02311613527120274</v>
       </c>
       <c r="H29">
-        <v>0.7166666666666666</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I29">
-        <v>0.06894263136661591</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J29">
-        <v>0.6668504901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K29">
-        <v>0.06119121789946656</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L29">
-        <v>0.6989115124641441</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M29">
-        <v>0.08874255287396449</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N29">
-        <v>0.6668504901960784</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O29">
-        <v>0.06119121789946656</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P29">
-        <v>0.6482310326233141</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q29">
-        <v>0.07337102114827743</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R29" t="s">
         <v>58</v>
@@ -2084,240 +2066,234 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="F30">
-        <v>0.8596680964052288</v>
+        <v>0.8921527777777779</v>
       </c>
       <c r="G30">
-        <v>0.03756383761162244</v>
+        <v>0.02225214998629001</v>
       </c>
       <c r="H30">
-        <v>0.7277777777777779</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="I30">
-        <v>0.04082482904638632</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J30">
-        <v>0.6849754901960783</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="K30">
-        <v>0.0547091738371323</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="L30">
-        <v>0.7086713286713288</v>
+        <v>0.7719642857142857</v>
       </c>
       <c r="M30">
-        <v>0.06312509762326829</v>
+        <v>0.1678725930072958</v>
       </c>
       <c r="N30">
-        <v>0.6849754901960783</v>
+        <v>0.7295833333333333</v>
       </c>
       <c r="O30">
-        <v>0.0547091738371323</v>
+        <v>0.07507403753036807</v>
       </c>
       <c r="P30">
-        <v>0.6753960592100924</v>
+        <v>0.7133820346320345</v>
       </c>
       <c r="Q30">
-        <v>0.05080763823283108</v>
+        <v>0.1225981326624976</v>
       </c>
       <c r="R30" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="F31">
-        <v>0.8568801062091502</v>
+        <v>0.8883333333333334</v>
       </c>
       <c r="G31">
-        <v>0.03643150649973629</v>
+        <v>0.03563088807741377</v>
       </c>
       <c r="H31">
-        <v>0.7222222222222223</v>
+        <v>0.711111111111111</v>
       </c>
       <c r="I31">
-        <v>0.04303314829119354</v>
+        <v>0.04157397096415492</v>
       </c>
       <c r="J31">
-        <v>0.6749754901960784</v>
+        <v>0.6920833333333333</v>
       </c>
       <c r="K31">
-        <v>0.04935943178221491</v>
+        <v>0.06487702041383975</v>
       </c>
       <c r="L31">
-        <v>0.702312162475206</v>
+        <v>0.7009126984126984</v>
       </c>
       <c r="M31">
-        <v>0.0672731256970306</v>
+        <v>0.1191710735538741</v>
       </c>
       <c r="N31">
-        <v>0.6749754901960784</v>
+        <v>0.6920833333333333</v>
       </c>
       <c r="O31">
-        <v>0.04935943178221491</v>
+        <v>0.06487702041383975</v>
       </c>
       <c r="P31">
-        <v>0.6602243380166993</v>
+        <v>0.6778163992869874</v>
       </c>
       <c r="Q31">
-        <v>0.0549625009335796</v>
+        <v>0.08198616730257983</v>
       </c>
       <c r="R31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>0.8564119689542483</v>
+        <v>0.8868402777777777</v>
       </c>
       <c r="G32">
-        <v>0.01466015171973254</v>
+        <v>0.02026969016798658</v>
       </c>
       <c r="H32">
-        <v>0.6777777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="I32">
-        <v>0.06478835438717</v>
+        <v>0.07535922203472517</v>
       </c>
       <c r="J32">
-        <v>0.5716176470588236</v>
+        <v>0.6649999999999998</v>
       </c>
       <c r="K32">
-        <v>0.07355556520172576</v>
+        <v>0.07219764539096821</v>
       </c>
       <c r="L32">
-        <v>0.4942824919823002</v>
+        <v>0.7057467532467533</v>
       </c>
       <c r="M32">
-        <v>0.05274189726988138</v>
+        <v>0.2008834053339353</v>
       </c>
       <c r="N32">
-        <v>0.5716176470588236</v>
+        <v>0.6649999999999998</v>
       </c>
       <c r="O32">
-        <v>0.07355556520172576</v>
+        <v>0.07219764539096821</v>
       </c>
       <c r="P32">
-        <v>0.5204604711164309</v>
+        <v>0.6425311384521911</v>
       </c>
       <c r="Q32">
-        <v>0.06663004832091855</v>
+        <v>0.1224152691762901</v>
       </c>
       <c r="R32" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>0.8488056576797387</v>
+        <v>0.8850694444444445</v>
       </c>
       <c r="G33">
-        <v>0.04051780175989513</v>
+        <v>0.03566092243463268</v>
       </c>
       <c r="H33">
-        <v>0.7277777777777779</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="I33">
-        <v>0.02721655269759088</v>
+        <v>0.05665577237325316</v>
       </c>
       <c r="J33">
-        <v>0.6701102941176471</v>
+        <v>0.65</v>
       </c>
       <c r="K33">
-        <v>0.05273801910547597</v>
+        <v>0.04031128874149275</v>
       </c>
       <c r="L33">
-        <v>0.633939393939394</v>
+        <v>0.5216269841269842</v>
       </c>
       <c r="M33">
-        <v>0.06595592205957784</v>
+        <v>0.05040057478866151</v>
       </c>
       <c r="N33">
-        <v>0.6701102941176471</v>
+        <v>0.65</v>
       </c>
       <c r="O33">
-        <v>0.05273801910547597</v>
+        <v>0.04031128874149275</v>
       </c>
       <c r="P33">
-        <v>0.6390991781104011</v>
+        <v>0.5686836855954504</v>
       </c>
       <c r="Q33">
-        <v>0.0510751344152194</v>
+        <v>0.05515085266240933</v>
       </c>
       <c r="R33" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>0.8471184640522876</v>
+        <v>0.8658333333333335</v>
       </c>
       <c r="G34">
-        <v>0.04256321492110534</v>
+        <v>0.0192820600431119</v>
       </c>
       <c r="H34">
-        <v>0.6222222222222223</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I34">
-        <v>0.2038215147538238</v>
+        <v>0.09938079899999065</v>
       </c>
       <c r="J34">
-        <v>0.6007843137254902</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="K34">
-        <v>0.1599922269218517</v>
+        <v>0.09414822828332398</v>
       </c>
       <c r="L34">
-        <v>0.6467910151284008</v>
+        <v>0.6129166666666667</v>
       </c>
       <c r="M34">
-        <v>0.1373591035265672</v>
+        <v>0.1530338556827697</v>
       </c>
       <c r="N34">
-        <v>0.6007843137254902</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="O34">
-        <v>0.1599922269218517</v>
+        <v>0.09414822828332398</v>
       </c>
       <c r="P34">
-        <v>0.5696668983820686</v>
+        <v>0.6271556956115779</v>
       </c>
       <c r="Q34">
-        <v>0.2115621263187106</v>
+        <v>0.1302373568714494</v>
       </c>
       <c r="R34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2325,43 +2301,43 @@
         <v>24</v>
       </c>
       <c r="F35">
-        <v>0.8461417483660132</v>
+        <v>0.8565277777777778</v>
       </c>
       <c r="G35">
-        <v>0.0380688783246222</v>
+        <v>0.03296757520140803</v>
       </c>
       <c r="H35">
-        <v>0.7</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I35">
-        <v>0.04082482904638632</v>
+        <v>0.07856742013183859</v>
       </c>
       <c r="J35">
-        <v>0.6518014705882352</v>
+        <v>0.6441666666666667</v>
       </c>
       <c r="K35">
-        <v>0.06186161864671579</v>
+        <v>0.07682275776819723</v>
       </c>
       <c r="L35">
-        <v>0.6175987056421839</v>
+        <v>0.5690079365079365</v>
       </c>
       <c r="M35">
-        <v>0.06394933378705091</v>
+        <v>0.1401354714743249</v>
       </c>
       <c r="N35">
-        <v>0.6518014705882352</v>
+        <v>0.6441666666666667</v>
       </c>
       <c r="O35">
-        <v>0.06186161864671579</v>
+        <v>0.07682275776819723</v>
       </c>
       <c r="P35">
-        <v>0.6218340367997118</v>
+        <v>0.5840777359895007</v>
       </c>
       <c r="Q35">
-        <v>0.06380586455557036</v>
+        <v>0.09756100175723413</v>
       </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2369,43 +2345,43 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>0.8438872549019608</v>
+        <v>0.8559722222222224</v>
       </c>
       <c r="G36">
-        <v>0.02590656205188437</v>
+        <v>0.03369354703623107</v>
       </c>
       <c r="H36">
-        <v>0.6833333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="I36">
-        <v>0.01360827634879544</v>
+        <v>0.07535922203472517</v>
       </c>
       <c r="J36">
-        <v>0.6538602941176471</v>
+        <v>0.7008333333333333</v>
       </c>
       <c r="K36">
-        <v>0.04316949900640113</v>
+        <v>0.07622381153185956</v>
       </c>
       <c r="L36">
-        <v>0.62963349387111</v>
+        <v>0.7068650793650793</v>
       </c>
       <c r="M36">
-        <v>0.05016830737319895</v>
+        <v>0.1409050712467391</v>
       </c>
       <c r="N36">
-        <v>0.6538602941176471</v>
+        <v>0.7008333333333333</v>
       </c>
       <c r="O36">
-        <v>0.04316949900640113</v>
+        <v>0.07622381153185956</v>
       </c>
       <c r="P36">
-        <v>0.6273834968885122</v>
+        <v>0.6721973941091588</v>
       </c>
       <c r="Q36">
-        <v>0.05023380621302379</v>
+        <v>0.1147968920646811</v>
       </c>
       <c r="R36" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2413,43 +2389,43 @@
         <v>26</v>
       </c>
       <c r="F37">
-        <v>0.8427369281045752</v>
+        <v>0.8525</v>
       </c>
       <c r="G37">
-        <v>0.03983607972901509</v>
+        <v>0.01048220125784067</v>
       </c>
       <c r="H37">
-        <v>0.7277777777777777</v>
+        <v>0.7</v>
       </c>
       <c r="I37">
-        <v>0.04779069592801461</v>
+        <v>0.07535922203472517</v>
       </c>
       <c r="J37">
-        <v>0.6799264705882353</v>
+        <v>0.7008333333333333</v>
       </c>
       <c r="K37">
-        <v>0.06643234844874314</v>
+        <v>0.07622381153185956</v>
       </c>
       <c r="L37">
-        <v>0.6671482683982684</v>
+        <v>0.7068650793650793</v>
       </c>
       <c r="M37">
-        <v>0.0627875135718468</v>
+        <v>0.1409050712467391</v>
       </c>
       <c r="N37">
-        <v>0.6799264705882353</v>
+        <v>0.7008333333333333</v>
       </c>
       <c r="O37">
-        <v>0.06643234844874314</v>
+        <v>0.07622381153185956</v>
       </c>
       <c r="P37">
-        <v>0.6572047935515427</v>
+        <v>0.6721973941091588</v>
       </c>
       <c r="Q37">
-        <v>0.0648323877049025</v>
+        <v>0.1147968920646811</v>
       </c>
       <c r="R37" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2457,43 +2433,43 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>0.8385633169934639</v>
+        <v>0.8462847222222223</v>
       </c>
       <c r="G38">
-        <v>0.01986157465959292</v>
+        <v>0.04289966739021829</v>
       </c>
       <c r="H38">
-        <v>0.711111111111111</v>
+        <v>0.7</v>
       </c>
       <c r="I38">
-        <v>0.05152010275275393</v>
+        <v>0.0753592220347252</v>
       </c>
       <c r="J38">
-        <v>0.6401593137254902</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="K38">
-        <v>0.05927289045643346</v>
+        <v>0.08196374537291197</v>
       </c>
       <c r="L38">
-        <v>0.6177864782276546</v>
+        <v>0.6552182539682539</v>
       </c>
       <c r="M38">
-        <v>0.08473958395298078</v>
+        <v>0.133433795061068</v>
       </c>
       <c r="N38">
-        <v>0.6401593137254902</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="O38">
-        <v>0.05927289045643346</v>
+        <v>0.08196374537291197</v>
       </c>
       <c r="P38">
-        <v>0.6092949960256462</v>
+        <v>0.6362618100853396</v>
       </c>
       <c r="Q38">
-        <v>0.07050813476363266</v>
+        <v>0.1174067217878383</v>
       </c>
       <c r="R38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2501,43 +2477,43 @@
         <v>28</v>
       </c>
       <c r="F39">
-        <v>0.8369707924836602</v>
+        <v>0.8403125000000001</v>
       </c>
       <c r="G39">
-        <v>0.04976995908970852</v>
+        <v>0.04137432163481044</v>
       </c>
       <c r="H39">
-        <v>0.7111111111111111</v>
+        <v>0.7</v>
       </c>
       <c r="I39">
-        <v>0.03767961101736262</v>
+        <v>0.07535922203472517</v>
       </c>
       <c r="J39">
-        <v>0.657610294117647</v>
+        <v>0.6941666666666666</v>
       </c>
       <c r="K39">
-        <v>0.03892575112115401</v>
+        <v>0.07563848594171858</v>
       </c>
       <c r="L39">
-        <v>0.6419941863691863</v>
+        <v>0.6592460317460318</v>
       </c>
       <c r="M39">
-        <v>0.05364551842620727</v>
+        <v>0.1511036704517329</v>
       </c>
       <c r="N39">
-        <v>0.657610294117647</v>
+        <v>0.6941666666666666</v>
       </c>
       <c r="O39">
-        <v>0.03892575112115401</v>
+        <v>0.07563848594171858</v>
       </c>
       <c r="P39">
-        <v>0.6328714442384774</v>
+        <v>0.6525004244121891</v>
       </c>
       <c r="Q39">
-        <v>0.03980840772232127</v>
+        <v>0.1177233363370575</v>
       </c>
       <c r="R39" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2545,43 +2521,43 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>0.8369707924836602</v>
+        <v>0.8403125000000001</v>
       </c>
       <c r="G40">
-        <v>0.04976995908970852</v>
+        <v>0.04137432163481044</v>
       </c>
       <c r="H40">
-        <v>0.7</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="I40">
-        <v>0.03239417719358502</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="J40">
-        <v>0.6819852941176471</v>
+        <v>0.695</v>
       </c>
       <c r="K40">
-        <v>0.06489246578033468</v>
+        <v>0.06802777210652851</v>
       </c>
       <c r="L40">
-        <v>0.6682270507270507</v>
+        <v>0.7031349206349207</v>
       </c>
       <c r="M40">
-        <v>0.04412900839626743</v>
+        <v>0.1016981042555419</v>
       </c>
       <c r="N40">
-        <v>0.6819852941176471</v>
+        <v>0.695</v>
       </c>
       <c r="O40">
-        <v>0.06489246578033468</v>
+        <v>0.06802777210652851</v>
       </c>
       <c r="P40">
-        <v>0.6623958938345215</v>
+        <v>0.6737912740853916</v>
       </c>
       <c r="Q40">
-        <v>0.05698707316405765</v>
+        <v>0.08643701883530713</v>
       </c>
       <c r="R40" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2589,43 +2565,43 @@
         <v>30</v>
       </c>
       <c r="F41">
-        <v>0.8233489583333334</v>
+        <v>0.8384722222222223</v>
       </c>
       <c r="G41">
-        <v>0.02853089440876138</v>
+        <v>0.03544144013739212</v>
       </c>
       <c r="H41">
-        <v>0.6944444444444444</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="I41">
-        <v>0.05826715823167511</v>
+        <v>0.090267093384844</v>
       </c>
       <c r="J41">
-        <v>0.6270343137254903</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="K41">
-        <v>0.04588215327487143</v>
+        <v>0.07854581111965452</v>
       </c>
       <c r="L41">
-        <v>0.6120255740636175</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="M41">
-        <v>0.07428767362385474</v>
+        <v>0.1019291742503886</v>
       </c>
       <c r="N41">
-        <v>0.6270343137254903</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="O41">
-        <v>0.04588215327487143</v>
+        <v>0.07854581111965452</v>
       </c>
       <c r="P41">
-        <v>0.6099078287183126</v>
+        <v>0.6844554791613615</v>
       </c>
       <c r="Q41">
-        <v>0.05327134509391227</v>
+        <v>0.09582779908946566</v>
       </c>
       <c r="R41" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2633,43 +2609,43 @@
         <v>31</v>
       </c>
       <c r="F42">
-        <v>0.8214758986928103</v>
+        <v>0.8384722222222223</v>
       </c>
       <c r="G42">
-        <v>0.04144913959992089</v>
+        <v>0.03544144013739212</v>
       </c>
       <c r="H42">
-        <v>0.6722222222222222</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42">
-        <v>0.04082482904638632</v>
+        <v>0.09938079899999065</v>
       </c>
       <c r="J42">
-        <v>0.6676102941176472</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="K42">
-        <v>0.06050418481194325</v>
+        <v>0.09414822828332398</v>
       </c>
       <c r="L42">
-        <v>0.646464674386501</v>
+        <v>0.6323809523809524</v>
       </c>
       <c r="M42">
-        <v>0.05890007382453428</v>
+        <v>0.1515550119353734</v>
       </c>
       <c r="N42">
-        <v>0.6676102941176472</v>
+        <v>0.6716666666666666</v>
       </c>
       <c r="O42">
-        <v>0.06050418481194325</v>
+        <v>0.09414822828332398</v>
       </c>
       <c r="P42">
-        <v>0.6455902344989032</v>
+        <v>0.6292895339954164</v>
       </c>
       <c r="Q42">
-        <v>0.06013027117832016</v>
+        <v>0.1297841289292717</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2677,43 +2653,43 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>0.8214758986928103</v>
+        <v>0.8261805555555556</v>
       </c>
       <c r="G43">
-        <v>0.04144913959992089</v>
+        <v>0.03296790433208306</v>
       </c>
       <c r="H43">
-        <v>0.6666666666666666</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="I43">
-        <v>0.01756820922315767</v>
+        <v>0.09558139185602918</v>
       </c>
       <c r="J43">
-        <v>0.6342769607843137</v>
+        <v>0.6466666666666667</v>
       </c>
       <c r="K43">
-        <v>0.02694274686285634</v>
+        <v>0.09243616415908029</v>
       </c>
       <c r="L43">
-        <v>0.6075190332543273</v>
+        <v>0.5660046897546896</v>
       </c>
       <c r="M43">
-        <v>0.04392128742319548</v>
+        <v>0.1632226049750582</v>
       </c>
       <c r="N43">
-        <v>0.6342769607843137</v>
+        <v>0.6466666666666667</v>
       </c>
       <c r="O43">
-        <v>0.02694274686285634</v>
+        <v>0.09243616415908029</v>
       </c>
       <c r="P43">
-        <v>0.6069283376686471</v>
+        <v>0.5809577200405374</v>
       </c>
       <c r="Q43">
-        <v>0.03318919069133781</v>
+        <v>0.1229362317891322</v>
       </c>
       <c r="R43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2721,43 +2697,43 @@
         <v>33</v>
       </c>
       <c r="F44">
-        <v>0.8192455065359476</v>
+        <v>0.8140277777777778</v>
       </c>
       <c r="G44">
-        <v>0.04810618969049924</v>
+        <v>0.02483898767345353</v>
       </c>
       <c r="H44">
-        <v>0.538888888888889</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="I44">
-        <v>0.2301368353023109</v>
+        <v>0.0816496580927726</v>
       </c>
       <c r="J44">
-        <v>0.5138848039215685</v>
+        <v>0.6375</v>
       </c>
       <c r="K44">
-        <v>0.1888602921296349</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="L44">
-        <v>0.5620999915117563</v>
+        <v>0.6341666666666665</v>
       </c>
       <c r="M44">
-        <v>0.2761897438940754</v>
+        <v>0.1062393118540399</v>
       </c>
       <c r="N44">
-        <v>0.5138848039215685</v>
+        <v>0.6375</v>
       </c>
       <c r="O44">
-        <v>0.1888602921296349</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="P44">
-        <v>0.4634236069078307</v>
+        <v>0.626499023851965</v>
       </c>
       <c r="Q44">
-        <v>0.2461910054103323</v>
+        <v>0.1025570250505807</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2765,43 +2741,43 @@
         <v>34</v>
       </c>
       <c r="F45">
-        <v>0.8121211192810458</v>
+        <v>0.7891666666666667</v>
       </c>
       <c r="G45">
-        <v>0.03834159851557533</v>
+        <v>0.01406554322352462</v>
       </c>
       <c r="H45">
-        <v>0.65</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="I45">
-        <v>0.05443310539518172</v>
+        <v>0.04444444444444443</v>
       </c>
       <c r="J45">
-        <v>0.6357107843137255</v>
+        <v>0.6837500000000001</v>
       </c>
       <c r="K45">
-        <v>0.08449051837690337</v>
+        <v>0.02109831483528694</v>
       </c>
       <c r="L45">
-        <v>0.6494884825319608</v>
+        <v>0.6816071428571429</v>
       </c>
       <c r="M45">
-        <v>0.05478450416834478</v>
+        <v>0.04982622864741507</v>
       </c>
       <c r="N45">
-        <v>0.6357107843137255</v>
+        <v>0.6837500000000001</v>
       </c>
       <c r="O45">
-        <v>0.08449051837690337</v>
+        <v>0.02109831483528694</v>
       </c>
       <c r="P45">
-        <v>0.6261770339933619</v>
+        <v>0.6707648968678379</v>
       </c>
       <c r="Q45">
-        <v>0.06719173992342302</v>
+        <v>0.02550130101086717</v>
       </c>
       <c r="R45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -2809,43 +2785,43 @@
         <v>35</v>
       </c>
       <c r="F46">
-        <v>0.757140522875817</v>
+        <v>0.7827777777777778</v>
       </c>
       <c r="G46">
-        <v>0.05632701225126891</v>
+        <v>0.1283609878813518</v>
       </c>
       <c r="H46">
-        <v>0.65</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I46">
-        <v>0.05443310539518172</v>
+        <v>0.2424158247696825</v>
       </c>
       <c r="J46">
-        <v>0.6357107843137255</v>
+        <v>0.5233333333333332</v>
       </c>
       <c r="K46">
-        <v>0.08449051837690337</v>
+        <v>0.1987565512547112</v>
       </c>
       <c r="L46">
-        <v>0.6494884825319608</v>
+        <v>0.4391369047619048</v>
       </c>
       <c r="M46">
-        <v>0.05478450416834478</v>
+        <v>0.3174496060940965</v>
       </c>
       <c r="N46">
-        <v>0.6357107843137255</v>
+        <v>0.5233333333333332</v>
       </c>
       <c r="O46">
-        <v>0.08449051837690337</v>
+        <v>0.1987565512547112</v>
       </c>
       <c r="P46">
-        <v>0.6261770339933619</v>
+        <v>0.4182678286625655</v>
       </c>
       <c r="Q46">
-        <v>0.06719173992342302</v>
+        <v>0.2630992213251235</v>
       </c>
       <c r="R46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2853,43 +2829,43 @@
         <v>36</v>
       </c>
       <c r="F47">
-        <v>0.757140522875817</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="G47">
-        <v>0.05632701225126891</v>
+        <v>0.06719696495203807</v>
       </c>
       <c r="H47">
-        <v>0.65</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="I47">
-        <v>0.05443310539518172</v>
+        <v>0.0816496580927726</v>
       </c>
       <c r="J47">
-        <v>0.6357107843137255</v>
+        <v>0.6375</v>
       </c>
       <c r="K47">
-        <v>0.08449051837690337</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="L47">
-        <v>0.6494884825319608</v>
+        <v>0.6341666666666665</v>
       </c>
       <c r="M47">
-        <v>0.05478450416834478</v>
+        <v>0.1062393118540399</v>
       </c>
       <c r="N47">
-        <v>0.6357107843137255</v>
+        <v>0.6375</v>
       </c>
       <c r="O47">
-        <v>0.08449051837690337</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="P47">
-        <v>0.6261770339933619</v>
+        <v>0.626499023851965</v>
       </c>
       <c r="Q47">
-        <v>0.06719173992342302</v>
+        <v>0.1025570250505807</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -2897,43 +2873,43 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>0.6940849673202615</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="G48">
-        <v>0.04888015567203923</v>
+        <v>0.06719696495203807</v>
       </c>
       <c r="H48">
-        <v>0.5888888888888889</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="I48">
-        <v>0.05386310952684809</v>
+        <v>0.0816496580927726</v>
       </c>
       <c r="J48">
-        <v>0.5411274509803921</v>
+        <v>0.6375</v>
       </c>
       <c r="K48">
-        <v>0.07332023350805887</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="L48">
-        <v>0.5580564138304076</v>
+        <v>0.6341666666666665</v>
       </c>
       <c r="M48">
-        <v>0.03600438570852901</v>
+        <v>0.1062393118540399</v>
       </c>
       <c r="N48">
-        <v>0.5411274509803921</v>
+        <v>0.6375</v>
       </c>
       <c r="O48">
-        <v>0.07332023350805887</v>
+        <v>0.1007954474280571</v>
       </c>
       <c r="P48">
-        <v>0.531808040413842</v>
+        <v>0.626499023851965</v>
       </c>
       <c r="Q48">
-        <v>0.04475022668769762</v>
+        <v>0.1025570250505807</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
